--- a/iShares/iShares-KostenBepaling2020.xlsx
+++ b/iShares/iShares-KostenBepaling2020.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\Aandelen\KeuzeWelkIndexFonds\PerFonds\iShares\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C551DB-1F23-412A-8489-5473F1571ECB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70C7BBA-13BF-4BFF-8C77-F0F5C904203D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aanames" sheetId="6" r:id="rId1"/>
@@ -315,13 +315,13 @@
     <t>4 basispunten er naast maar, niet onaardig</t>
   </si>
   <si>
-    <t>gok dat door niet instant herinvesteren dividend komt of wat optimized gebeuren</t>
-  </si>
-  <si>
     <t>6 basispunten er naast maar, niet onaardig</t>
   </si>
   <si>
     <t>Optimized selectie, heeft 3303/4263 posities dus tracking diff bekijken geen nut</t>
+  </si>
+  <si>
+    <t>wel gek dat ik meer kosten vind als de tracking difference</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="I13" s="29"/>
       <c r="K13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="G11" s="2"/>
       <c r="I11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="G12" s="2"/>
       <c r="I12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -2605,7 +2605,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">

--- a/iShares/iShares-KostenBepaling2020.xlsx
+++ b/iShares/iShares-KostenBepaling2020.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\Aandelen\KeuzeWelkIndexFonds\PerFonds\iShares\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70C7BBA-13BF-4BFF-8C77-F0F5C904203D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA6C052-EEFD-4527-8CD7-CC5780BE141D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="74">
   <si>
     <t>Transaction costs</t>
   </si>
@@ -298,9 +298,6 @@
   </si>
   <si>
     <t>De TER gaat weinig omlaag ook al neemt het vermogen fors toe</t>
-  </si>
-  <si>
-    <t>TER teruggerekend</t>
   </si>
   <si>
     <t>Gemiddeld vermogen via TER (operation expense) teruggerekend</t>
@@ -802,7 +799,7 @@
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
@@ -1023,46 +1020,40 @@
       <c r="I8" s="29"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="30">
-        <f>C6/C8</f>
-        <v>3.8999999999999998E-3</v>
-      </c>
-      <c r="D9" s="30">
-        <f t="shared" ref="D9:H9" si="1">D6/D8</f>
-        <v>2E-3</v>
-      </c>
-      <c r="E9" s="30">
-        <f t="shared" si="1"/>
-        <v>2E-3</v>
-      </c>
-      <c r="F9" s="30">
-        <f t="shared" si="1"/>
-        <v>2E-3</v>
-      </c>
-      <c r="G9" s="30">
-        <f t="shared" si="1"/>
-        <v>2E-3</v>
-      </c>
-      <c r="H9" s="30">
-        <f t="shared" si="1"/>
-        <v>2E-3</v>
-      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
       <c r="I9" s="29"/>
       <c r="K9" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
+      <c r="B10" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="21">
+        <v>21877</v>
+      </c>
+      <c r="D10" s="21">
+        <v>68989</v>
+      </c>
+      <c r="E10" s="22">
+        <v>146778</v>
+      </c>
+      <c r="F10" s="22">
+        <v>218802</v>
+      </c>
+      <c r="G10" s="22">
+        <v>323631</v>
+      </c>
+      <c r="H10" s="22">
+        <v>435291</v>
+      </c>
       <c r="I10" s="29"/>
       <c r="K10" s="2" t="s">
         <v>45</v>
@@ -1070,305 +1061,296 @@
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C11" s="21">
-        <v>21877</v>
+        <v>2530</v>
       </c>
       <c r="D11" s="21">
-        <v>68989</v>
+        <v>7895</v>
       </c>
       <c r="E11" s="22">
-        <v>146778</v>
+        <v>17329</v>
       </c>
       <c r="F11" s="22">
-        <v>218802</v>
+        <v>25220</v>
       </c>
       <c r="G11" s="22">
-        <v>323631</v>
+        <v>37451</v>
       </c>
       <c r="H11" s="22">
-        <v>435291</v>
+        <v>51767</v>
       </c>
       <c r="I11" s="29"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="21">
-        <v>2530</v>
-      </c>
-      <c r="D12" s="21">
-        <v>7895</v>
-      </c>
-      <c r="E12" s="22">
-        <v>17329</v>
-      </c>
-      <c r="F12" s="22">
-        <v>25220</v>
-      </c>
-      <c r="G12" s="22">
-        <v>37451</v>
-      </c>
-      <c r="H12" s="22">
-        <v>51767</v>
+        <v>10</v>
+      </c>
+      <c r="C12" s="24">
+        <f>C11/C10</f>
+        <v>0.11564656945650684</v>
+      </c>
+      <c r="D12" s="24">
+        <f t="shared" ref="D12:H12" si="1">D11/D10</f>
+        <v>0.11443853367928221</v>
+      </c>
+      <c r="E12" s="24">
+        <f t="shared" si="1"/>
+        <v>0.11806265244110153</v>
+      </c>
+      <c r="F12" s="24">
+        <f t="shared" si="1"/>
+        <v>0.11526402866518587</v>
+      </c>
+      <c r="G12" s="24">
+        <f t="shared" si="1"/>
+        <v>0.11572129987547547</v>
+      </c>
+      <c r="H12" s="24">
+        <f t="shared" si="1"/>
+        <v>0.11892504094961762</v>
       </c>
       <c r="I12" s="29"/>
       <c r="K12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="24">
-        <f>C12/C11</f>
-        <v>0.11564656945650684</v>
-      </c>
-      <c r="D13" s="24">
-        <f t="shared" ref="D13:H13" si="2">D12/D11</f>
-        <v>0.11443853367928221</v>
-      </c>
-      <c r="E13" s="24">
-        <f t="shared" si="2"/>
-        <v>0.11806265244110153</v>
-      </c>
-      <c r="F13" s="24">
-        <f t="shared" si="2"/>
-        <v>0.11526402866518587</v>
-      </c>
-      <c r="G13" s="24">
-        <f t="shared" si="2"/>
-        <v>0.11572129987547547</v>
-      </c>
-      <c r="H13" s="24">
-        <f t="shared" si="2"/>
-        <v>0.11892504094961762</v>
-      </c>
-      <c r="I13" s="29"/>
+        <v>29</v>
+      </c>
+      <c r="C13" s="30">
+        <f>C11/C8</f>
+        <v>2.9339875111507579E-3</v>
+      </c>
+      <c r="D13" s="30">
+        <f>D11/D8</f>
+        <v>2.9508503083535789E-3</v>
+      </c>
+      <c r="E13" s="30">
+        <f>E11/E8</f>
+        <v>3.2198067632850241E-3</v>
+      </c>
+      <c r="F13" s="30">
+        <f>F11/F8</f>
+        <v>2.9423088140932158E-3</v>
+      </c>
+      <c r="G13" s="30">
+        <f>G11/G8</f>
+        <v>2.8010171646535285E-3</v>
+      </c>
+      <c r="H13" s="30">
+        <f>H11/H8</f>
+        <v>3.004033077034673E-3</v>
+      </c>
+      <c r="I13" s="29">
+        <f>AVERAGE(C13:H13)</f>
+        <v>2.9753339397617963E-3</v>
+      </c>
       <c r="K13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="30">
-        <f t="shared" ref="C14:H14" si="3">C12/C8</f>
-        <v>2.9339875111507579E-3</v>
-      </c>
-      <c r="D14" s="30">
-        <f t="shared" si="3"/>
-        <v>2.9508503083535789E-3</v>
-      </c>
-      <c r="E14" s="30">
-        <f t="shared" si="3"/>
-        <v>3.2198067632850241E-3</v>
-      </c>
-      <c r="F14" s="30">
-        <f t="shared" si="3"/>
-        <v>2.9423088140932158E-3</v>
-      </c>
-      <c r="G14" s="30">
-        <f t="shared" si="3"/>
-        <v>2.8010171646535285E-3</v>
-      </c>
-      <c r="H14" s="30">
-        <f t="shared" si="3"/>
-        <v>3.004033077034673E-3</v>
-      </c>
-      <c r="I14" s="29">
-        <f>AVERAGE(C14:H14)</f>
-        <v>2.9753339397617963E-3</v>
-      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="29"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="20"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
+      <c r="B15" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="21">
+        <v>7</v>
+      </c>
+      <c r="D15" s="21">
+        <v>349</v>
+      </c>
+      <c r="E15" s="22">
+        <v>947</v>
+      </c>
+      <c r="F15" s="22">
+        <v>2133</v>
+      </c>
+      <c r="G15" s="22">
+        <v>3345</v>
+      </c>
+      <c r="H15" s="22">
+        <v>5560</v>
+      </c>
       <c r="I15" s="29"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="21">
-        <v>7</v>
-      </c>
-      <c r="D16" s="21">
-        <v>349</v>
-      </c>
-      <c r="E16" s="22">
-        <v>947</v>
-      </c>
-      <c r="F16" s="22">
-        <v>2133</v>
-      </c>
-      <c r="G16" s="22">
-        <v>3345</v>
-      </c>
-      <c r="H16" s="22">
-        <v>5560</v>
-      </c>
-      <c r="I16" s="29"/>
+        <v>21</v>
+      </c>
+      <c r="C16" s="25">
+        <f>C15/C8</f>
+        <v>8.1177520071364855E-6</v>
+      </c>
+      <c r="D16" s="25">
+        <f>D15/D8</f>
+        <v>1.3044290786768829E-4</v>
+      </c>
+      <c r="E16" s="25">
+        <f>E15/E8</f>
+        <v>1.759568933481977E-4</v>
+      </c>
+      <c r="F16" s="25">
+        <f>F15/F8</f>
+        <v>2.4884792626728109E-4</v>
+      </c>
+      <c r="G16" s="25">
+        <f>G15/G8</f>
+        <v>2.5017762985677424E-4</v>
+      </c>
+      <c r="H16" s="25">
+        <f>H15/H8</f>
+        <v>3.2264616277382854E-4</v>
+      </c>
+      <c r="I16" s="29">
+        <f>AVERAGE(C16:H16)</f>
+        <v>1.893648786868177E-4</v>
+      </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="25">
-        <f t="shared" ref="C17:H17" si="4">C16/C8</f>
-        <v>8.1177520071364855E-6</v>
-      </c>
-      <c r="D17" s="25">
-        <f t="shared" si="4"/>
-        <v>1.3044290786768829E-4</v>
-      </c>
-      <c r="E17" s="25">
-        <f t="shared" si="4"/>
-        <v>1.759568933481977E-4</v>
-      </c>
-      <c r="F17" s="25">
-        <f t="shared" si="4"/>
-        <v>2.4884792626728109E-4</v>
-      </c>
-      <c r="G17" s="25">
-        <f t="shared" si="4"/>
-        <v>2.5017762985677424E-4</v>
-      </c>
-      <c r="H17" s="25">
-        <f t="shared" si="4"/>
-        <v>3.2264616277382854E-4</v>
-      </c>
-      <c r="I17" s="29">
-        <f>AVERAGE(C17:H17)</f>
-        <v>1.893648786868177E-4</v>
-      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="29"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="20"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
+      <c r="B18" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="20">
+        <v>611</v>
+      </c>
+      <c r="D18" s="21">
+        <v>1652</v>
+      </c>
+      <c r="E18" s="22">
+        <v>1649</v>
+      </c>
+      <c r="F18" s="22">
+        <v>2396</v>
+      </c>
+      <c r="G18" s="22">
+        <v>2254</v>
+      </c>
+      <c r="H18" s="22">
+        <v>2701</v>
+      </c>
       <c r="I18" s="29"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C19" s="20">
-        <v>611</v>
-      </c>
-      <c r="D19" s="21">
-        <v>1652</v>
-      </c>
-      <c r="E19" s="22">
-        <v>1649</v>
-      </c>
-      <c r="F19" s="22">
-        <v>2396</v>
-      </c>
-      <c r="G19" s="22">
-        <v>2254</v>
-      </c>
-      <c r="H19" s="22">
-        <v>2701</v>
-      </c>
-      <c r="I19" s="29"/>
+        <v>1</v>
+      </c>
+      <c r="C19" s="30">
+        <f>C18/C8</f>
+        <v>7.0856378233719887E-4</v>
+      </c>
+      <c r="D19" s="30">
+        <f>D18/D8</f>
+        <v>6.1745468136796859E-4</v>
+      </c>
+      <c r="E19" s="30">
+        <f>E18/E8</f>
+        <v>3.0639167595689337E-4</v>
+      </c>
+      <c r="F19" s="30">
+        <f>F18/F8</f>
+        <v>2.7953100390830078E-4</v>
+      </c>
+      <c r="G19" s="30">
+        <f>G18/G8</f>
+        <v>1.685800830185857E-4</v>
+      </c>
+      <c r="H19" s="30">
+        <f>H18/H8</f>
+        <v>1.5673872044102714E-4</v>
+      </c>
+      <c r="I19" s="29">
+        <f>AVERAGE(C19:H19)</f>
+        <v>3.7287665783832907E-4</v>
+      </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" s="30">
-        <f t="shared" ref="C20:H20" si="5">C19/C8</f>
-        <v>7.0856378233719887E-4</v>
-      </c>
-      <c r="D20" s="30">
-        <f t="shared" si="5"/>
-        <v>6.1745468136796859E-4</v>
-      </c>
-      <c r="E20" s="30">
-        <f t="shared" si="5"/>
-        <v>3.0639167595689337E-4</v>
-      </c>
-      <c r="F20" s="30">
-        <f t="shared" si="5"/>
-        <v>2.7953100390830078E-4</v>
-      </c>
-      <c r="G20" s="30">
-        <f t="shared" si="5"/>
-        <v>1.685800830185857E-4</v>
-      </c>
-      <c r="H20" s="30">
-        <f t="shared" si="5"/>
-        <v>1.5673872044102714E-4</v>
-      </c>
-      <c r="I20" s="29">
-        <f>AVERAGE(C20:H20)</f>
-        <v>3.7287665783832907E-4</v>
-      </c>
+      <c r="B20" s="20"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="29"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="20"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="29"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="26"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="B22" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="29">
+        <f>I7+I13-I16+I19</f>
+        <v>5.4755123855799743E-3</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
       <c r="I22" s="26"/>
       <c r="K22" s="8"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C23" s="29">
-        <f>I7+I14-I17+I20</f>
-        <v>5.4755123855799743E-3</v>
-      </c>
-      <c r="D23" s="18" t="s">
+        <f>TrackingDifference!K5/100</f>
+        <v>5.0499999999999989E-3</v>
+      </c>
+      <c r="D23" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
       <c r="K23" s="8"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="18" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C24" s="29">
-        <f>TrackingDifference!K5/100</f>
-        <v>5.0499999999999989E-3</v>
-      </c>
-      <c r="D24" t="s">
-        <v>51</v>
-      </c>
+        <f>C23-C22</f>
+        <v>-4.2551238557997535E-4</v>
+      </c>
+      <c r="D24" s="18"/>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
       <c r="G24" s="18"/>
@@ -1377,13 +1359,7 @@
       <c r="K24" s="8"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="29">
-        <f>C24-C23</f>
-        <v>-4.2551238557997535E-4</v>
-      </c>
+      <c r="C25" s="18"/>
       <c r="D25" s="18"/>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
@@ -1394,24 +1370,17 @@
       <c r="K25" s="8"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
+      <c r="B26" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="31">
+        <f>H7+I13-G16+H19</f>
+        <v>4.8818950303460493E-3</v>
+      </c>
       <c r="J26" s="6"/>
       <c r="K26" s="8"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" s="31">
-        <f>H7+I14-G17+H20</f>
-        <v>4.8818950303460493E-3</v>
-      </c>
       <c r="J27" s="6"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
@@ -1598,7 +1567,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85662431-B8A3-40F8-9BF4-EC97DECEFC14}">
-  <dimension ref="A2:I27"/>
+  <dimension ref="A2:I26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.5703125" customWidth="1"/>
@@ -1650,7 +1619,7 @@
         <v>2</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1755,288 +1724,274 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="4">
-        <f>B6/B8</f>
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="C9" s="4">
-        <f t="shared" ref="C9:F9" si="1">C6/C8</f>
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="D9" s="4">
-        <f t="shared" si="1"/>
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="E9" s="4">
-        <f t="shared" si="1"/>
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="F9" s="4">
-        <f t="shared" si="1"/>
-        <v>1.8E-3</v>
-      </c>
+      <c r="A9" s="20"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
       <c r="G9" s="2"/>
       <c r="I9" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="16">
+        <v>4988</v>
+      </c>
+      <c r="C10" s="16">
+        <v>34764</v>
+      </c>
+      <c r="D10" s="16">
+        <v>79612</v>
+      </c>
+      <c r="E10" s="16">
+        <v>172015</v>
+      </c>
+      <c r="F10" s="16">
+        <v>276851</v>
+      </c>
       <c r="G10" s="2"/>
       <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11" s="16">
-        <v>4988</v>
+        <v>661</v>
       </c>
       <c r="C11" s="16">
-        <v>34764</v>
+        <v>3983</v>
       </c>
       <c r="D11" s="16">
-        <v>79612</v>
+        <v>10068</v>
       </c>
       <c r="E11" s="16">
-        <v>172015</v>
+        <v>21696</v>
       </c>
       <c r="F11" s="16">
-        <v>276851</v>
+        <v>38608</v>
       </c>
       <c r="G11" s="2"/>
       <c r="I11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="16">
-        <v>661</v>
-      </c>
-      <c r="C12" s="16">
-        <v>3983</v>
-      </c>
-      <c r="D12" s="16">
-        <v>10068</v>
-      </c>
-      <c r="E12" s="16">
-        <v>21696</v>
-      </c>
-      <c r="F12" s="16">
-        <v>38608</v>
+        <v>10</v>
+      </c>
+      <c r="B12" s="33">
+        <f t="shared" ref="B12:F12" si="1">B11/B10</f>
+        <v>0.13251804330392944</v>
+      </c>
+      <c r="C12" s="33">
+        <f t="shared" si="1"/>
+        <v>0.11457254631227706</v>
+      </c>
+      <c r="D12" s="33">
+        <f t="shared" si="1"/>
+        <v>0.12646334723408531</v>
+      </c>
+      <c r="E12" s="33">
+        <f t="shared" si="1"/>
+        <v>0.12612853530215387</v>
+      </c>
+      <c r="F12" s="33">
+        <f t="shared" si="1"/>
+        <v>0.13945407457441006</v>
       </c>
       <c r="G12" s="2"/>
       <c r="I12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="33">
-        <f t="shared" ref="B13:F13" si="2">B12/B11</f>
-        <v>0.13251804330392944</v>
-      </c>
-      <c r="C13" s="33">
-        <f t="shared" si="2"/>
-        <v>0.11457254631227706</v>
-      </c>
-      <c r="D13" s="33">
-        <f t="shared" si="2"/>
-        <v>0.12646334723408531</v>
-      </c>
-      <c r="E13" s="33">
-        <f t="shared" si="2"/>
-        <v>0.12612853530215387</v>
-      </c>
-      <c r="F13" s="33">
-        <f t="shared" si="2"/>
-        <v>0.13945407457441006</v>
-      </c>
-      <c r="G13" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="B13" s="17">
+        <f>B11/B8</f>
+        <v>2.1657929226736568E-3</v>
+      </c>
+      <c r="C13" s="17">
+        <f>C11/C8</f>
+        <v>3.1293211816467632E-3</v>
+      </c>
+      <c r="D13" s="17">
+        <f>D11/D8</f>
+        <v>3.1074074074074073E-3</v>
+      </c>
+      <c r="E13" s="17">
+        <f>E11/E8</f>
+        <v>3.0807679200272635E-3</v>
+      </c>
+      <c r="F13" s="17">
+        <f>F11/F8</f>
+        <v>3.4937609974360264E-3</v>
+      </c>
+      <c r="G13" s="36">
+        <f>AVERAGE(B13:F13)</f>
+        <v>2.9954100858382232E-3</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="17">
-        <f>B12/B8</f>
-        <v>2.1657929226736568E-3</v>
-      </c>
-      <c r="C14" s="17">
-        <f t="shared" ref="C14:F14" si="3">C12/C8</f>
-        <v>3.1293211816467632E-3</v>
-      </c>
-      <c r="D14" s="17">
-        <f t="shared" si="3"/>
-        <v>3.1074074074074073E-3</v>
-      </c>
-      <c r="E14" s="17">
-        <f t="shared" si="3"/>
-        <v>3.0807679200272635E-3</v>
-      </c>
-      <c r="F14" s="17">
-        <f t="shared" si="3"/>
-        <v>3.4937609974360264E-3</v>
-      </c>
-      <c r="G14" s="36">
-        <f>AVERAGE(B14:F14)</f>
-        <v>2.9954100858382232E-3</v>
-      </c>
+      <c r="A14" s="2"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="2"/>
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
+      <c r="A15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="16">
+        <v>29</v>
+      </c>
+      <c r="C15" s="16">
+        <v>610</v>
+      </c>
+      <c r="D15" s="16">
+        <v>4933</v>
+      </c>
+      <c r="E15" s="16">
+        <v>9146</v>
+      </c>
+      <c r="F15" s="16">
+        <v>10433</v>
+      </c>
       <c r="G15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="16">
-        <v>29</v>
-      </c>
-      <c r="C16" s="16">
-        <v>610</v>
-      </c>
-      <c r="D16" s="16">
-        <v>4933</v>
-      </c>
-      <c r="E16" s="16">
-        <v>9146</v>
-      </c>
-      <c r="F16" s="16">
-        <v>10433</v>
-      </c>
-      <c r="G16" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B16" s="17">
+        <f>B15/B8</f>
+        <v>9.5019659239842721E-5</v>
+      </c>
+      <c r="C16" s="17">
+        <f>C15/C8</f>
+        <v>4.7925832809553738E-4</v>
+      </c>
+      <c r="D16" s="17">
+        <f>D15/D8</f>
+        <v>1.5225308641975308E-3</v>
+      </c>
+      <c r="E16" s="17">
+        <f>E15/E8</f>
+        <v>1.2987049869362718E-3</v>
+      </c>
+      <c r="F16" s="17">
+        <f>F15/F8</f>
+        <v>9.4411542908853243E-4</v>
+      </c>
+      <c r="G16" s="36">
+        <f>AVERAGE(B16:F16)</f>
+        <v>8.6792585351154299E-4</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="17">
-        <f>B16/B8</f>
-        <v>9.5019659239842721E-5</v>
-      </c>
-      <c r="C17" s="17">
-        <f t="shared" ref="C17:F17" si="4">C16/C8</f>
-        <v>4.7925832809553738E-4</v>
-      </c>
-      <c r="D17" s="17">
-        <f t="shared" si="4"/>
-        <v>1.5225308641975308E-3</v>
-      </c>
-      <c r="E17" s="17">
-        <f t="shared" si="4"/>
-        <v>1.2987049869362718E-3</v>
-      </c>
-      <c r="F17" s="17">
-        <f t="shared" si="4"/>
-        <v>9.4411542908853243E-4</v>
-      </c>
-      <c r="G17" s="36">
-        <f>AVERAGE(B17:F17)</f>
-        <v>8.6792585351154299E-4</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
+      <c r="A18" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="16">
+        <v>875</v>
+      </c>
+      <c r="C18" s="16">
+        <v>1451</v>
+      </c>
+      <c r="D18" s="16">
+        <v>2644</v>
+      </c>
       <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
+      <c r="F18" s="16">
+        <v>5320</v>
+      </c>
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="16">
-        <v>875</v>
-      </c>
-      <c r="C19" s="16">
-        <v>1451</v>
-      </c>
-      <c r="D19" s="16">
-        <v>2644</v>
-      </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16">
-        <v>5320</v>
-      </c>
-      <c r="G19" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B19" s="17">
+        <f>B18/B8</f>
+        <v>2.8669724770642203E-3</v>
+      </c>
+      <c r="C19" s="17">
+        <f>C18/C8</f>
+        <v>1.1400062853551226E-3</v>
+      </c>
+      <c r="D19" s="17">
+        <f>D18/D8</f>
+        <v>8.160493827160494E-4</v>
+      </c>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17">
+        <f>F18/F8</f>
+        <v>4.8142375948921623E-4</v>
+      </c>
+      <c r="G19" s="36">
+        <f>AVERAGE(B19:F19)</f>
+        <v>1.326112976156152E-3</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="17">
-        <f t="shared" ref="B20:F20" si="5">B19/B8</f>
-        <v>2.8669724770642203E-3</v>
-      </c>
-      <c r="C20" s="17">
-        <f t="shared" si="5"/>
-        <v>1.1400062853551226E-3</v>
-      </c>
-      <c r="D20" s="17">
-        <f t="shared" si="5"/>
-        <v>8.160493827160494E-4</v>
-      </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17">
-        <f t="shared" si="5"/>
-        <v>4.8142375948921623E-4</v>
-      </c>
-      <c r="G20" s="36">
-        <f>AVERAGE(B20:F20)</f>
-        <v>1.326112976156152E-3</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
+      <c r="A21" s="1"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
+      <c r="A22" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="7">
+        <f>G7+G13-G16+G19</f>
+        <v>5.8135972084828319E-3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
       <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" s="7">
-        <f>G7+G14-G17+G20</f>
-        <v>5.8135972084828319E-3</v>
+        <f>TrackingDifference!K12/100</f>
+        <v>5.1800000000000136E-3</v>
       </c>
       <c r="C23" t="s">
         <v>50</v>
@@ -2044,32 +1999,20 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="B24" s="7">
-        <f>TrackingDifference!K12/100</f>
-        <v>5.1800000000000136E-3</v>
-      </c>
-      <c r="C24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="7">
-        <f>B24-B23</f>
+        <f>B23-B22</f>
         <v>-6.3359720848281832E-4</v>
       </c>
-      <c r="C25" s="18"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="C24" s="18"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="32">
-        <f>F7+G14-G17+AVERAGE(D20:F20)</f>
+      <c r="B26" s="32">
+        <f>F7+G13-G16+AVERAGE(D19:F19)</f>
         <v>4.5762208034293133E-3</v>
       </c>
     </row>
@@ -2539,7 +2482,7 @@
         <v>49</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
@@ -2605,7 +2548,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">

--- a/iShares/iShares-KostenBepaling2020.xlsx
+++ b/iShares/iShares-KostenBepaling2020.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\Aandelen\KeuzeWelkIndexFonds\PerFonds\iShares\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA6C052-EEFD-4527-8CD7-CC5780BE141D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAEA5C7-8B8A-453D-96EE-410F0381460C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aanames" sheetId="6" r:id="rId1"/>
     <sheet name="IWDA" sheetId="1" r:id="rId2"/>
     <sheet name="EMIM" sheetId="4" r:id="rId3"/>
-    <sheet name="IEMS" sheetId="2" r:id="rId4"/>
-    <sheet name="IUSN" sheetId="3" r:id="rId5"/>
-    <sheet name="TrackingDifference" sheetId="5" r:id="rId6"/>
+    <sheet name="Emerging" sheetId="7" r:id="rId4"/>
+    <sheet name="IEMS" sheetId="2" r:id="rId5"/>
+    <sheet name="IUSN" sheetId="3" r:id="rId6"/>
+    <sheet name="TrackingDifference" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -96,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="75">
   <si>
     <t>Transaction costs</t>
   </si>
@@ -319,6 +320,9 @@
   </si>
   <si>
     <t>wel gek dat ik meer kosten vind als de tracking difference</t>
+  </si>
+  <si>
+    <t>andere emerging</t>
   </si>
 </sst>
 </file>
@@ -416,7 +420,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -426,6 +430,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,7 +454,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -504,6 +514,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Procent" xfId="1" builtinId="5"/>
@@ -1121,27 +1132,27 @@
         <v>29</v>
       </c>
       <c r="C13" s="30">
-        <f>C11/C8</f>
+        <f t="shared" ref="C13:H13" si="2">C11/C8</f>
         <v>2.9339875111507579E-3</v>
       </c>
       <c r="D13" s="30">
-        <f>D11/D8</f>
+        <f t="shared" si="2"/>
         <v>2.9508503083535789E-3</v>
       </c>
       <c r="E13" s="30">
-        <f>E11/E8</f>
+        <f t="shared" si="2"/>
         <v>3.2198067632850241E-3</v>
       </c>
       <c r="F13" s="30">
-        <f>F11/F8</f>
+        <f t="shared" si="2"/>
         <v>2.9423088140932158E-3</v>
       </c>
       <c r="G13" s="30">
-        <f>G11/G8</f>
+        <f t="shared" si="2"/>
         <v>2.8010171646535285E-3</v>
       </c>
       <c r="H13" s="30">
-        <f>H11/H8</f>
+        <f t="shared" si="2"/>
         <v>3.004033077034673E-3</v>
       </c>
       <c r="I13" s="29">
@@ -2023,6 +2034,21 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16348FBD-6D4E-468D-BBE5-71CE4F661AE0}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46EB2121-1E5C-40E6-84C9-729FC25AD7CB}">
   <dimension ref="B2:K26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2481,7 +2507,7 @@
       <c r="B23" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="49" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2506,7 +2532,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3319A48F-C74C-4C2A-9714-F1A50A94B19B}">
   <dimension ref="A2:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2836,7 +2862,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045330D2-0890-4532-8ABA-CDB206A2E066}">
   <dimension ref="B1:M19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/iShares/iShares-KostenBepaling2020.xlsx
+++ b/iShares/iShares-KostenBepaling2020.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\Aandelen\KeuzeWelkIndexFonds\PerFonds\iShares\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAEA5C7-8B8A-453D-96EE-410F0381460C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB752457-9600-4159-A4A8-06E26C9A5093}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aanames" sheetId="6" r:id="rId1"/>
@@ -454,7 +454,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -515,6 +515,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Procent" xfId="1" builtinId="5"/>
@@ -1122,7 +1123,10 @@
         <f t="shared" si="1"/>
         <v>0.11892504094961762</v>
       </c>
-      <c r="I12" s="29"/>
+      <c r="I12" s="29">
+        <f>AVERAGE(C12:H12)</f>
+        <v>0.11634302084452826</v>
+      </c>
       <c r="K12" t="s">
         <v>70</v>
       </c>
@@ -1202,27 +1206,27 @@
         <v>21</v>
       </c>
       <c r="C16" s="25">
-        <f>C15/C8</f>
+        <f t="shared" ref="C16:H16" si="3">C15/C8</f>
         <v>8.1177520071364855E-6</v>
       </c>
       <c r="D16" s="25">
-        <f>D15/D8</f>
+        <f t="shared" si="3"/>
         <v>1.3044290786768829E-4</v>
       </c>
       <c r="E16" s="25">
-        <f>E15/E8</f>
+        <f t="shared" si="3"/>
         <v>1.759568933481977E-4</v>
       </c>
       <c r="F16" s="25">
-        <f>F15/F8</f>
+        <f t="shared" si="3"/>
         <v>2.4884792626728109E-4</v>
       </c>
       <c r="G16" s="25">
-        <f>G15/G8</f>
+        <f t="shared" si="3"/>
         <v>2.5017762985677424E-4</v>
       </c>
       <c r="H16" s="25">
-        <f>H15/H8</f>
+        <f t="shared" si="3"/>
         <v>3.2264616277382854E-4</v>
       </c>
       <c r="I16" s="29">
@@ -1269,27 +1273,27 @@
         <v>1</v>
       </c>
       <c r="C19" s="30">
-        <f>C18/C8</f>
+        <f t="shared" ref="C19:H19" si="4">C18/C8</f>
         <v>7.0856378233719887E-4</v>
       </c>
       <c r="D19" s="30">
-        <f>D18/D8</f>
+        <f t="shared" si="4"/>
         <v>6.1745468136796859E-4</v>
       </c>
       <c r="E19" s="30">
-        <f>E18/E8</f>
+        <f t="shared" si="4"/>
         <v>3.0639167595689337E-4</v>
       </c>
       <c r="F19" s="30">
-        <f>F18/F8</f>
+        <f t="shared" si="4"/>
         <v>2.7953100390830078E-4</v>
       </c>
       <c r="G19" s="30">
-        <f>G18/G8</f>
+        <f t="shared" si="4"/>
         <v>1.685800830185857E-4</v>
       </c>
       <c r="H19" s="30">
-        <f>H18/H8</f>
+        <f t="shared" si="4"/>
         <v>1.5673872044102714E-4</v>
       </c>
       <c r="I19" s="29">
@@ -1816,7 +1820,10 @@
         <f t="shared" si="1"/>
         <v>0.13945407457441006</v>
       </c>
-      <c r="G12" s="2"/>
+      <c r="G12" s="50">
+        <f>AVERAGE(B12:F12)</f>
+        <v>0.12782730934537115</v>
+      </c>
       <c r="I12" t="s">
         <v>73</v>
       </c>

--- a/iShares/iShares-KostenBepaling2020.xlsx
+++ b/iShares/iShares-KostenBepaling2020.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\iShares\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59BFD1B4-5558-4975-AA61-50E78506495B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DFDCBB-3BE0-4C2D-A4F0-228EBBA4B69D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11775" yWindow="1830" windowWidth="38535" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aanames" sheetId="6" r:id="rId1"/>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="137">
   <si>
     <t>Transaction costs</t>
   </si>
@@ -513,9 +513,6 @@
     <t>2015 startjaar?</t>
   </si>
   <si>
-    <t>Lek wat lager</t>
-  </si>
-  <si>
     <t>2016-2019</t>
   </si>
   <si>
@@ -523,6 +520,15 @@
   </si>
   <si>
     <t>Dividend</t>
+  </si>
+  <si>
+    <t>Cap</t>
+  </si>
+  <si>
+    <t>Market cap %</t>
+  </si>
+  <si>
+    <t>Lek wat lager, dividend wat hoger</t>
   </si>
 </sst>
 </file>
@@ -651,7 +657,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -718,6 +724,8 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Komma" xfId="3" builtinId="3"/>
@@ -2047,7 +2055,12 @@
       <c r="C3" s="49"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C4" s="49"/>
+      <c r="C4" s="56" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>135</v>
+      </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -2057,7 +2070,7 @@
       <c r="C5" s="49">
         <v>41819772.990000002</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="4">
         <v>0.7782992046811118</v>
       </c>
       <c r="G5" s="4"/>
@@ -2069,7 +2082,7 @@
       <c r="C6" s="49">
         <v>5480574.1299999999</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="4">
         <v>0.10199783933774233</v>
       </c>
       <c r="G6" s="4"/>
@@ -2081,7 +2094,7 @@
       <c r="C7" s="49">
         <v>5789028.6699999999</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="4">
         <v>0.10773842342029304</v>
       </c>
       <c r="G7" s="4"/>
@@ -2093,7 +2106,7 @@
       <c r="C8" s="49">
         <v>642881.34999999963</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="4">
         <v>1.1964532746960738E-2</v>
       </c>
       <c r="G8" s="6"/>
@@ -2137,7 +2150,7 @@
       <c r="G15" s="7"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -2182,15 +2195,15 @@
       </c>
       <c r="C19" s="7">
         <f>EMIM!B28</f>
-        <v>4.8596253582531028E-3</v>
+        <v>4.719058311055754E-3</v>
       </c>
       <c r="D19" s="7">
         <f>EMIM!B30</f>
-        <v>1.7865761391385232E-3</v>
+        <v>1.6460090919411742E-3</v>
       </c>
       <c r="E19" s="7">
         <f>EMIM!B32</f>
-        <v>4.1159964771545279E-3</v>
+        <v>3.9754294299571792E-3</v>
       </c>
       <c r="F19" s="14">
         <f>EMIM!G12</f>
@@ -2285,7 +2298,7 @@
       </c>
       <c r="C27" s="5">
         <f>C18*D5+C19*(D7+D8)+C23*D6</f>
-        <v>5.0227750726781319E-3</v>
+        <v>5.005948781588907E-3</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
@@ -2294,7 +2307,7 @@
       </c>
       <c r="C28" s="5">
         <f>E18*D5+E19*(D7+D8)+E23*D6</f>
-        <v>4.5515856263715574E-3</v>
+        <v>4.5347593352823325E-3</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
@@ -2308,7 +2321,7 @@
       </c>
       <c r="C31" s="5">
         <f>D18*D5+D19*(D7+D8)+D23*D6</f>
-        <v>2.0587008587619757E-3</v>
+        <v>2.0418745676727508E-3</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
@@ -2329,7 +2342,7 @@
       </c>
       <c r="C33" s="6">
         <f>SUM(C31:C32)</f>
-        <v>5.0256293461869378E-3</v>
+        <v>5.0088030550977129E-3</v>
       </c>
     </row>
   </sheetData>
@@ -2659,7 +2672,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B14" s="29">
         <f>B10/B8</f>
@@ -2728,27 +2741,27 @@
       <c r="A17" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="57">
         <f t="shared" ref="B17:G17" si="4">B16/B8</f>
         <v>8.1177520071364855E-6</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="57">
         <f t="shared" si="4"/>
         <v>1.3044290786768829E-4</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="57">
         <f t="shared" si="4"/>
         <v>1.759568933481977E-4</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="57">
         <f t="shared" si="4"/>
         <v>2.4884792626728109E-4</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="57">
         <f t="shared" si="4"/>
         <v>2.5017762985677424E-4</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="57">
         <f t="shared" si="4"/>
         <v>3.2264616277382854E-4</v>
       </c>
@@ -3588,20 +3601,20 @@
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="32">
         <f>B19/B8</f>
         <v>2.8669724770642203E-3</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="32">
         <f>C19/C8</f>
         <v>1.1400062853551226E-3</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="32">
         <f>D19/D8</f>
         <v>8.160493827160494E-4</v>
       </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17">
+      <c r="E20" s="32"/>
+      <c r="F20" s="32">
         <f>F19/F8</f>
         <v>5.3491528832135134E-4</v>
       </c>
@@ -3689,8 +3702,8 @@
         <v>3</v>
       </c>
       <c r="B28" s="30">
-        <f>F7+G13-G16+AVERAGE(D20:F20)</f>
-        <v>4.8596253582531028E-3</v>
+        <f>F7+G13-G16+F20</f>
+        <v>4.719058311055754E-3</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -3699,7 +3712,7 @@
       </c>
       <c r="B29" s="34">
         <f>B28-B24</f>
-        <v>-1.0640035228454857E-3</v>
+        <v>-1.2045705700428344E-3</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -3707,8 +3720,8 @@
         <v>112</v>
       </c>
       <c r="B30" s="7">
-        <f>F7-G16+AVERAGE(D20:F20)</f>
-        <v>1.7865761391385232E-3</v>
+        <f>F7-G16+F20</f>
+        <v>1.6460090919411742E-3</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -3717,7 +3730,7 @@
       </c>
       <c r="B32" s="30">
         <f>B25+B29</f>
-        <v>4.1159964771545279E-3</v>
+        <v>3.9754294299571792E-3</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -5905,7 +5918,7 @@
         <v>2019</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I4" t="s">
         <v>127</v>
@@ -6009,7 +6022,7 @@
       </c>
       <c r="G8" s="7"/>
       <c r="I8" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -6326,7 +6339,7 @@
         <v>7.6092256916506958E-3</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -6338,7 +6351,7 @@
         <v>6.6249999999999963E-3</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -6359,7 +6372,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="30">
-        <f>F7+AVERAGE(C13:F13)+AVERAGE(F21)-AVERAGE(F17)</f>
+        <f>F7++G13-F17+F21</f>
         <v>7.3818776066824493E-3</v>
       </c>
     </row>

--- a/iShares/iShares-KostenBepaling2020.xlsx
+++ b/iShares/iShares-KostenBepaling2020.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\iShares\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DFDCBB-3BE0-4C2D-A4F0-228EBBA4B69D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560AA5D6-9741-473F-B0CA-AD5777D29F6E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aanames" sheetId="6" r:id="rId1"/>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="138">
   <si>
     <t>Transaction costs</t>
   </si>
@@ -381,9 +381,6 @@
     <t>2014-2019</t>
   </si>
   <si>
-    <t>Gemiddelde (2015-2019)</t>
-  </si>
-  <si>
     <t>Dividend lek wisselt nogal</t>
   </si>
   <si>
@@ -529,6 +526,12 @@
   </si>
   <si>
     <t>Lek wat lager, dividend wat hoger</t>
+  </si>
+  <si>
+    <t>Boekjaar anders dan kalenderjaar!</t>
+  </si>
+  <si>
+    <t>2015-2020</t>
   </si>
 </sst>
 </file>
@@ -657,7 +660,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -726,6 +729,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Komma" xfId="3" builtinId="3"/>
@@ -1116,7 +1120,7 @@
         <v>2019</v>
       </c>
       <c r="J1" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K1" s="37"/>
       <c r="L1" s="35" t="s">
@@ -1654,7 +1658,7 @@
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E29">
         <v>-15.34</v>
@@ -1785,7 +1789,7 @@
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E36">
         <v>-15.33</v>
@@ -1910,7 +1914,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43" s="35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E43">
         <v>-3.27</v>
@@ -1930,7 +1934,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44" s="35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E44">
         <v>-2.73</v>
@@ -1950,7 +1954,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45" s="35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E45">
         <v>-3.28</v>
@@ -2056,10 +2060,10 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C4" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="F4" s="1"/>
     </row>
@@ -2151,25 +2155,25 @@
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C18" s="7">
         <f>IWDA!B29</f>
@@ -2191,47 +2195,47 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C19" s="7">
         <f>EMIM!B28</f>
-        <v>4.719058311055754E-3</v>
+        <v>4.4786061793558284E-3</v>
       </c>
       <c r="D19" s="7">
         <f>EMIM!B30</f>
-        <v>1.6460090919411742E-3</v>
+        <v>1.3203125018091872E-3</v>
       </c>
       <c r="E19" s="7">
         <f>EMIM!B32</f>
-        <v>3.9754294299571792E-3</v>
+        <v>3.9380063083695798E-3</v>
       </c>
       <c r="F19" s="14">
-        <f>EMIM!G12</f>
-        <v>0.12782730934537115</v>
+        <f>EMIM!H12</f>
+        <v>0.12767451727949905</v>
       </c>
       <c r="H19" s="7"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C20" s="7">
         <f>IEMM!B28</f>
-        <v>4.9214957171222831E-3</v>
+        <v>1.1411843296331416E-2</v>
       </c>
       <c r="E20" s="7">
         <f>IEMM!B31</f>
-        <v>4.932642487809797E-3</v>
+        <v>1.0872684125879233E-2</v>
       </c>
       <c r="F20" s="14">
-        <f>IEMM!H12</f>
-        <v>0.12203008604052865</v>
+        <f>IEMM!I12</f>
+        <v>0.13496071550767211</v>
       </c>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C21" s="7">
         <f>IEMA!B28</f>
@@ -2249,7 +2253,7 @@
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C22" s="7">
         <f>IEMS!B28</f>
@@ -2267,7 +2271,7 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C23" s="7">
         <f>IUSN!B28</f>
@@ -2275,7 +2279,7 @@
       </c>
       <c r="D23" s="7">
         <f>IUSN!B29</f>
-        <v>3.5389713679745494E-3</v>
+        <v>3.5389713679745498E-3</v>
       </c>
       <c r="E23" s="7">
         <f>IUSN!B31</f>
@@ -2289,16 +2293,16 @@
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C27" s="5">
         <f>C18*D5+C19*(D7+D8)+C23*D6</f>
-        <v>5.005948781588907E-3</v>
+        <v>4.9771659506077084E-3</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
@@ -2307,42 +2311,42 @@
       </c>
       <c r="C28" s="5">
         <f>E18*D5+E19*(D7+D8)+E23*D6</f>
-        <v>4.5347593352823325E-3</v>
+        <v>4.5302796769992907E-3</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C31" s="5">
         <f>D18*D5+D19*(D7+D8)+D23*D6</f>
-        <v>2.0418745676727508E-3</v>
+        <v>2.0028877230203581E-3</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C32" s="5">
         <f>(F18*D5+F19*(D7+D8)+F23*D6)*2.5%</f>
-        <v>2.9669284874249621E-3</v>
+        <v>2.9664712458758679E-3</v>
       </c>
       <c r="D32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C33" s="6">
         <f>SUM(C31:C32)</f>
-        <v>5.0088030550977129E-3</v>
+        <v>4.9693589688962255E-3</v>
       </c>
     </row>
   </sheetData>
@@ -2672,7 +2676,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B14" s="29">
         <f>B10/B8</f>
@@ -2700,7 +2704,7 @@
       </c>
       <c r="H14" s="48"/>
       <c r="J14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -2736,6 +2740,9 @@
         <v>5560</v>
       </c>
       <c r="H16" s="28"/>
+      <c r="J16" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
@@ -2992,10 +2999,10 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B31" s="30">
-        <f>G7-F17+G21</f>
+        <f>B29-H13</f>
         <v>1.906561090584253E-3</v>
       </c>
       <c r="C31" s="12"/>
@@ -3209,17 +3216,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85662431-B8A3-40F8-9BF4-EC97DECEFC14}">
-  <dimension ref="A2:I36"/>
+  <dimension ref="A2:J36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.5703125" customWidth="1"/>
-    <col min="2" max="6" width="17.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" customWidth="1"/>
-    <col min="9" max="9" width="104.85546875" customWidth="1"/>
+    <col min="2" max="7" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="10" max="10" width="104.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>38</v>
       </c>
@@ -3229,19 +3236,20 @@
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
-      <c r="I2" s="1" t="s">
+      <c r="H2" s="9"/>
+      <c r="J2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="50" t="s">
+      <c r="J3" s="50" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>2015</v>
       </c>
@@ -3257,12 +3265,15 @@
       <c r="F4" s="1">
         <v>2019</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="33"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="33"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -3281,12 +3292,15 @@
       <c r="F5" s="16">
         <v>12495330</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="I5" s="2" t="s">
+      <c r="G5" s="16">
+        <v>14157723</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="J5" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -3305,12 +3319,15 @@
       <c r="F6" s="16">
         <v>19891</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="I6" s="2" t="s">
+      <c r="G6" s="16">
+        <v>24296</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="J6" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -3329,20 +3346,23 @@
       <c r="F7" s="17">
         <v>2E-3</v>
       </c>
-      <c r="G7" s="34">
-        <f>AVERAGE(B7:F7)</f>
-        <v>2.4000000000000002E-3</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="G7" s="17">
+        <v>1.8E-3</v>
+      </c>
+      <c r="H7" s="34">
+        <f>AVERAGE(B7:G7)</f>
+        <v>2.3E-3</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="16">
-        <f t="shared" ref="B8:F8" si="0">B6/B7</f>
+        <f t="shared" ref="B8:G8" si="0">B6/B7</f>
         <v>305200</v>
       </c>
       <c r="C8" s="16">
@@ -3361,22 +3381,27 @@
         <f t="shared" si="0"/>
         <v>9945500</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="I8" s="2" t="s">
+      <c r="G8" s="16">
+        <f t="shared" si="0"/>
+        <v>13497777.777777778</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="J8" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="20"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="2"/>
-      <c r="I9" s="8"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G9" s="4"/>
+      <c r="H9" s="2"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -3395,12 +3420,15 @@
       <c r="F10" s="16">
         <v>276851</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="I10" t="s">
+      <c r="G10" s="16">
+        <v>381237</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="J10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -3419,17 +3447,20 @@
       <c r="F11" s="16">
         <v>38608</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="I11" t="s">
+      <c r="G11" s="16">
+        <v>48383</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="J11" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="31">
-        <f t="shared" ref="B12:F12" si="1">B11/B10</f>
+        <f t="shared" ref="B12:G12" si="1">B11/B10</f>
         <v>0.13251804330392944</v>
       </c>
       <c r="C12" s="31">
@@ -3448,15 +3479,19 @@
         <f t="shared" si="1"/>
         <v>0.13945407457441006</v>
       </c>
-      <c r="G12" s="47">
-        <f>AVERAGE(B12:F12)</f>
-        <v>0.12782730934537115</v>
-      </c>
-      <c r="I12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G12" s="31">
+        <f t="shared" si="1"/>
+        <v>0.12691055695013861</v>
+      </c>
+      <c r="H12" s="47">
+        <f>AVERAGE(B12:G12)</f>
+        <v>0.12767451727949905</v>
+      </c>
+      <c r="J12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
@@ -3480,22 +3515,29 @@
         <f>F11/F8</f>
         <v>3.8819566638178069E-3</v>
       </c>
-      <c r="G13" s="34">
-        <f>AVERAGE(B13:F13)</f>
-        <v>3.0730492191145794E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G13" s="17">
+        <f>G11/G8</f>
+        <v>3.5845159697069475E-3</v>
+      </c>
+      <c r="H13" s="34">
+        <f>AVERAGE(B13:G13)</f>
+        <v>3.1582936775466411E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
-      <c r="G14" s="2"/>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G14" s="16"/>
+      <c r="H14" s="2"/>
+      <c r="J14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
@@ -3514,10 +3556,13 @@
       <c r="F15" s="16">
         <v>10433</v>
       </c>
-      <c r="G15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G15" s="16">
+        <v>12223</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -3541,12 +3586,16 @@
         <f>F15/F8</f>
         <v>1.0490171434317027E-3</v>
       </c>
-      <c r="G16" s="34">
-        <f>AVERAGE(B16:F16)</f>
-        <v>8.8890619638017716E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G16" s="17">
+        <f>G15/G8</f>
+        <v>9.0555647020085608E-4</v>
+      </c>
+      <c r="H16" s="34">
+        <f>AVERAGE(B16:G16)</f>
+        <v>8.9168124201695689E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>78</v>
       </c>
@@ -3567,18 +3616,22 @@
       <c r="F17" s="31">
         <v>0.1174</v>
       </c>
-      <c r="G17" s="34"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G17" s="31">
+        <v>0.1027</v>
+      </c>
+      <c r="H17" s="34"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="16"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G18" s="16"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>0</v>
       </c>
@@ -3595,9 +3648,12 @@
       <c r="F19" s="16">
         <v>5320</v>
       </c>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G19" s="16">
+        <v>5561</v>
+      </c>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
@@ -3618,12 +3674,16 @@
         <f>F19/F8</f>
         <v>5.3491528832135134E-4</v>
       </c>
-      <c r="G20" s="34">
-        <f>AVERAGE(B20:F20)</f>
-        <v>1.3394858583641858E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G20" s="32">
+        <f>G19/G8</f>
+        <v>4.1199374382614422E-4</v>
+      </c>
+      <c r="H20" s="34">
+        <f>AVERAGE(B20:G20)</f>
+        <v>1.1539874354565775E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -3631,8 +3691,9 @@
       <c r="E21" s="32"/>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H21" s="32"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>77</v>
       </c>
@@ -3651,9 +3712,12 @@
       <c r="F22" s="4">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G22" s="4">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -3661,21 +3725,22 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>44</v>
       </c>
       <c r="B24" s="7">
-        <f>G7+G13-G16+G20</f>
-        <v>5.9236288810985884E-3</v>
+        <f>H7+H13-H16+H20</f>
+        <v>5.7205998709862621E-3</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
-      </c>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>45</v>
       </c>
@@ -3684,56 +3749,56 @@
         <v>5.1800000000000136E-3</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="7">
         <f>B25-B24</f>
-        <v>-7.4362888109857483E-4</v>
+        <v>-5.4059987098624852E-4</v>
       </c>
       <c r="C26" s="18"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B28" s="30">
-        <f>F7+G13-G16+F20</f>
-        <v>4.719058311055754E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <f>G7+H13-H16+G20</f>
+        <v>4.4786061793558284E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B29" s="34">
         <f>B28-B24</f>
-        <v>-1.2045705700428344E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>-1.2419936916304337E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B30" s="7">
-        <f>F7-G16+F20</f>
-        <v>1.6460090919411742E-3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <f>B28-H13</f>
+        <v>1.3203125018091872E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B32" s="30">
         <f>B25+B29</f>
-        <v>3.9754294299571792E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3.9380063083695798E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>79</v>
       </c>
@@ -3750,8 +3815,9 @@
       <c r="F35" s="54">
         <v>492</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G35" s="54"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>80</v>
       </c>
@@ -3772,6 +3838,7 @@
         <f>F35/F8</f>
         <v>4.9469609371072343E-5</v>
       </c>
+      <c r="G36" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3786,7 +3853,7 @@
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
     <col min="2" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" customWidth="1"/>
     <col min="9" max="9" width="13.28515625" customWidth="1"/>
     <col min="10" max="10" width="91.85546875" customWidth="1"/>
   </cols>
@@ -3811,7 +3878,7 @@
         <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -3834,7 +3901,7 @@
         <v>2019</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>87</v>
+        <v>2</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>30</v>
@@ -3953,7 +4020,7 @@
       </c>
       <c r="H8" s="30"/>
       <c r="J8" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -4017,7 +4084,7 @@
       </c>
       <c r="H11" s="7"/>
       <c r="J11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -4053,7 +4120,7 @@
         <v>0.14642301968419308</v>
       </c>
       <c r="J12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -4089,7 +4156,7 @@
         <v>3.5453259492307376E-3</v>
       </c>
       <c r="J13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -4125,6 +4192,9 @@
         <v>2187</v>
       </c>
       <c r="H15" s="7"/>
+      <c r="J15" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -4450,7 +4520,9 @@
         <f>AVERAGE(B7:C7)</f>
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
@@ -4670,11 +4742,11 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B29" s="4">
-        <f>D7-C16+C20</f>
-        <v>3.5389713679745494E-3</v>
+        <f>B28-C13</f>
+        <v>3.5389713679745498E-3</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -4689,7 +4761,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B31" s="15">
         <f>B28-0.05%</f>
@@ -4740,19 +4812,19 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C9A39DF-ECA7-4B8A-BED1-414B316C3BE0}">
-  <dimension ref="A2:J31"/>
+  <dimension ref="A2:K31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
-    <col min="2" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1"/>
-    <col min="10" max="10" width="91.85546875" customWidth="1"/>
+    <col min="2" max="8" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="91.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="9"/>
@@ -4761,19 +4833,20 @@
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
-      <c r="J2" s="1" t="s">
+      <c r="I2" s="9"/>
+      <c r="K2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>2014</v>
       </c>
@@ -4792,14 +4865,17 @@
       <c r="G4" s="1">
         <v>2019</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H4" s="1">
+        <v>2020</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -4821,10 +4897,13 @@
       <c r="G5" s="11">
         <v>5078010</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H5" s="11">
+        <v>2778602</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -4846,11 +4925,14 @@
       <c r="G6" s="11">
         <v>40293</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H6" s="16">
+        <v>29657</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -4872,13 +4954,16 @@
       <c r="G7" s="17">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="H7" s="7">
-        <f>AVERAGE(C7:G7)</f>
+      <c r="H7" s="17">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I7" s="7">
+        <f>AVERAGE(C7:H7)</f>
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -4887,7 +4972,7 @@
         <v>5718133.333333334</v>
       </c>
       <c r="C8" s="11">
-        <f t="shared" ref="C8:G8" si="0">C6/C7</f>
+        <f t="shared" ref="C8:H8" si="0">C6/C7</f>
         <v>5611600</v>
       </c>
       <c r="D8" s="11">
@@ -4906,21 +4991,26 @@
         <f t="shared" si="0"/>
         <v>5372400</v>
       </c>
-      <c r="H8" s="30"/>
-      <c r="J8" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H8" s="11">
+        <f t="shared" si="0"/>
+        <v>3954266.666666667</v>
+      </c>
+      <c r="I8" s="30"/>
+      <c r="K8" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="30"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H9" s="1"/>
+      <c r="I9" s="30"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -4942,9 +5032,15 @@
       <c r="G10" s="11">
         <v>152689</v>
       </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H10" s="16">
+        <v>115503</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="K10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -4966,14 +5062,17 @@
       <c r="G11" s="11">
         <v>21015</v>
       </c>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H11" s="58">
+        <v>23056</v>
+      </c>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="14">
-        <f t="shared" ref="B12:G12" si="1">B11/B10</f>
+        <f t="shared" ref="B12:H12" si="1">B11/B10</f>
         <v>0.11358557309654983</v>
       </c>
       <c r="C12" s="14">
@@ -4996,12 +5095,16 @@
         <f t="shared" si="1"/>
         <v>0.13763270438603958</v>
       </c>
-      <c r="H12" s="7">
-        <f>AVERAGE(C12:G12)</f>
-        <v>0.12203008604052865</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H12" s="14">
+        <f t="shared" si="1"/>
+        <v>0.19961386284338936</v>
+      </c>
+      <c r="I12" s="7">
+        <f>AVERAGE(C12:H12)</f>
+        <v>0.13496071550767211</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>28</v>
       </c>
@@ -5010,7 +5113,7 @@
         <v>3.3243366133470127E-3</v>
       </c>
       <c r="C13" s="4">
-        <f t="shared" ref="C13:G13" si="2">C11/C8</f>
+        <f t="shared" ref="C13:H13" si="2">C11/C8</f>
         <v>3.1131940979399813E-3</v>
       </c>
       <c r="D13" s="4">
@@ -5029,12 +5132,16 @@
         <f t="shared" si="2"/>
         <v>3.9116595934777752E-3</v>
       </c>
-      <c r="H13" s="7">
-        <f>AVERAGE(C13:G13)</f>
-        <v>3.3982428143466111E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H13" s="4">
+        <f t="shared" si="2"/>
+        <v>5.8306639242000202E-3</v>
+      </c>
+      <c r="I13" s="7">
+        <f>AVERAGE(C13:H13)</f>
+        <v>3.8036463326555129E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -5042,9 +5149,10 @@
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H14" s="11"/>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
@@ -5066,9 +5174,12 @@
       <c r="G15" s="11">
         <v>3477</v>
       </c>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H15" s="16">
+        <v>1895</v>
+      </c>
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -5081,7 +5192,7 @@
         <v>5.4102216836552849E-4</v>
       </c>
       <c r="D16" s="17">
-        <f t="shared" ref="D16:G16" si="3">D15/D8</f>
+        <f t="shared" ref="D16:H16" si="3">D15/D8</f>
         <v>8.7031214547340441E-4</v>
       </c>
       <c r="E16" s="17">
@@ -5096,12 +5207,16 @@
         <f t="shared" si="3"/>
         <v>6.4719678356041995E-4</v>
       </c>
-      <c r="H16" s="7">
-        <f>AVERAGE(C16:G16)</f>
-        <v>6.6245013809355002E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H16" s="17">
+        <f t="shared" si="3"/>
+        <v>4.7922918703847316E-4</v>
+      </c>
+      <c r="I16" s="7">
+        <f>AVERAGE(C16:H16)</f>
+        <v>6.319133129177038E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>78</v>
       </c>
@@ -5126,9 +5241,12 @@
       <c r="G17" s="31">
         <v>0.12590000000000001</v>
       </c>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H17" s="31">
+        <v>0.1069</v>
+      </c>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -5136,9 +5254,10 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H18" s="11"/>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>0</v>
       </c>
@@ -5158,9 +5277,12 @@
       <c r="G19" s="11">
         <v>1766</v>
       </c>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H19" s="16">
+        <v>4584</v>
+      </c>
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
@@ -5169,7 +5291,7 @@
         <v>1.2761157487291889E-3</v>
       </c>
       <c r="C20" s="4">
-        <f t="shared" ref="C20:G20" si="4">C19/C8</f>
+        <f t="shared" ref="C20:H20" si="4">C19/C8</f>
         <v>7.6698267873690211E-4</v>
       </c>
       <c r="D20" s="4">
@@ -5188,17 +5310,21 @@
         <f t="shared" si="4"/>
         <v>3.2871714689896507E-4</v>
       </c>
-      <c r="H20" s="7">
-        <f>AVERAGE(C20:G20)</f>
-        <v>4.7306055305942896E-4</v>
-      </c>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H21" s="5"/>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H20" s="4">
+        <f t="shared" si="4"/>
+        <v>1.1592541389891088E-3</v>
+      </c>
+      <c r="I20" s="7">
+        <f>AVERAGE(C20:H20)</f>
+        <v>5.874261507143756E-4</v>
+      </c>
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I21" s="5"/>
+      <c r="K21" s="8"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>77</v>
       </c>
@@ -5218,10 +5344,13 @@
       <c r="G22" s="29">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="H22" s="5"/>
-      <c r="J22" s="8"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H22" s="29">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="I22" s="5"/>
+      <c r="K22" s="8"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -5230,21 +5359,22 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
-      <c r="J23" s="8"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I23" s="5"/>
+      <c r="K23" s="8"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>44</v>
       </c>
       <c r="B24" s="28">
-        <f>H7+H13-H16+H20</f>
-        <v>1.0708853229312488E-2</v>
+        <f>I7+I13-I16+I20</f>
+        <v>1.1259159170452185E-2</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>45</v>
       </c>
@@ -5253,54 +5383,55 @@
         <v>1.0720000000000002E-2</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="28">
         <f>B25-B24</f>
-        <v>1.1146770687513879E-5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-5.3915917045218274E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="18"/>
       <c r="B27" s="18"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B28" s="30">
-        <f>0.18%+AVERAGE(B13:G13)+G20-AVERAGE(F16:G16)</f>
-        <v>4.9214957171222831E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <f>H7+I13-H16+I20</f>
+        <v>1.1411843296331416E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B29" s="7">
         <f>B28-B24</f>
-        <v>-5.7873575121902051E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1.526841258792308E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B31" s="30">
         <f>B25+B29</f>
-        <v>4.932642487809797E-3</v>
+        <v>1.0872684125879233E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5311,14 +5442,14 @@
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
     <col min="2" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" customWidth="1"/>
     <col min="9" max="9" width="13.28515625" customWidth="1"/>
     <col min="10" max="10" width="91.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="9"/>
@@ -5336,7 +5467,7 @@
         <v>19</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -5359,7 +5490,7 @@
         <v>2019</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>87</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5410,7 +5541,7 @@
         <v>4948</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -5470,7 +5601,9 @@
         <v>727647.0588235294</v>
       </c>
       <c r="H8" s="30"/>
-      <c r="J8" s="2"/>
+      <c r="J8" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
@@ -5881,7 +6014,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="9"/>
@@ -5895,10 +6028,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -5918,10 +6051,10 @@
         <v>2019</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -5966,7 +6099,7 @@
         <v>4812</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -5993,7 +6126,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -6022,7 +6155,7 @@
       </c>
       <c r="G8" s="7"/>
       <c r="I8" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -6053,6 +6186,9 @@
         <v>56439</v>
       </c>
       <c r="G10" s="7"/>
+      <c r="I10" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
@@ -6135,7 +6271,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B14" s="4">
         <f>B10/B8</f>
@@ -6339,7 +6475,7 @@
         <v>7.6092256916506958E-3</v>
       </c>
       <c r="C25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -6351,7 +6487,7 @@
         <v>6.6249999999999963E-3</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">

--- a/iShares/iShares-KostenBepaling2020.xlsx
+++ b/iShares/iShares-KostenBepaling2020.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\iShares\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsen/KeuzeWelkIndexFonds/OnderzoekPerFonds/iShares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560AA5D6-9741-473F-B0CA-AD5777D29F6E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{A6ACE176-4C08-4AFF-ACEF-0847542540D3}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{37CF9434-8F84-4266-A9E4-E879F436B0AF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aanames" sheetId="6" r:id="rId1"/>
@@ -49,9 +49,9 @@
   <commentList>
     <comment ref="A7" authorId="0" shapeId="0" xr:uid="{475E6311-0448-49A0-9829-FF385283029D}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     6. OPERATING EXPENSES</t>
       </text>
     </comment>
@@ -538,13 +538,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="44" formatCode="_ &quot;€&quot;\ * #,##0.00_ ;_ &quot;€&quot;\ * \-#,##0.00_ ;_ &quot;€&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_ &quot;€&quot;\ * #,##0_ ;_ &quot;€&quot;\ * \-#,##0_ ;_ &quot;€&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ [$€-413]\ * #,##0_ ;_ [$€-413]\ * \-#,##0_ ;_ [$€-413]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -660,7 +661,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -730,12 +731,15 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Komma" xfId="3" builtinId="3"/>
-    <cellStyle name="Procent" xfId="1" builtinId="5"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
-    <cellStyle name="Valuta" xfId="2" builtinId="4"/>
+    <cellStyle name="Comma" xfId="3" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2177,19 +2181,19 @@
       </c>
       <c r="C18" s="7">
         <f>IWDA!B29</f>
-        <v>4.8818950303460493E-3</v>
+        <v>4.8160560860628652E-3</v>
       </c>
       <c r="D18" s="7">
         <f>IWDA!B31</f>
-        <v>1.906561090584253E-3</v>
+        <v>1.8608314711153389E-3</v>
       </c>
       <c r="E18" s="7">
         <f>IWDA!B33</f>
-        <v>4.4563826447660739E-3</v>
+        <v>4.501988307397565E-3</v>
       </c>
       <c r="F18" s="14">
-        <f>IWDA!H12</f>
-        <v>0.11634302084452826</v>
+        <f>IWDA!I12</f>
+        <v>0.11813180456504087</v>
       </c>
       <c r="H18" s="7"/>
     </row>
@@ -2239,15 +2243,15 @@
       </c>
       <c r="C21" s="7">
         <f>IEMA!B28</f>
-        <v>5.7099486057513279E-3</v>
+        <v>5.6395368492800409E-3</v>
       </c>
       <c r="E21" s="7">
         <f>IEMA!B31</f>
-        <v>5.0578330750149893E-3</v>
+        <v>5.8880853206998689E-3</v>
       </c>
       <c r="F21" s="14">
-        <f>IEMA!H12</f>
-        <v>0.12818992219549338</v>
+        <f>IEMA!I12</f>
+        <v>0.13091428836130456</v>
       </c>
       <c r="H21" s="7"/>
     </row>
@@ -2257,15 +2261,15 @@
       </c>
       <c r="C22" s="7">
         <f>IEMS!B28</f>
-        <v>6.8196709936002003E-3</v>
+        <v>7.0185445283327264E-3</v>
       </c>
       <c r="E22" s="7">
         <f>IEMS!B31</f>
-        <v>4.6282955167536617E-3</v>
+        <v>4.6104515530258783E-3</v>
       </c>
       <c r="F22" s="14">
-        <f>IEMS!H12</f>
-        <v>0.14642301968419308</v>
+        <f>IEMS!I12</f>
+        <v>0.14928432060421487</v>
       </c>
       <c r="H22" s="7"/>
     </row>
@@ -2275,19 +2279,19 @@
       </c>
       <c r="C23" s="7">
         <f>IUSN!B28</f>
-        <v>6.2892364793213154E-3</v>
+        <v>6.4432218800610881E-3</v>
       </c>
       <c r="D23" s="7">
         <f>IUSN!B29</f>
-        <v>3.5389713679745498E-3</v>
+        <v>3.6929567687143225E-3</v>
       </c>
       <c r="E23" s="7">
         <f>IUSN!B31</f>
-        <v>5.789236479321315E-3</v>
+        <v>5.9432218800610885E-3</v>
       </c>
       <c r="F23" s="14">
-        <f>IUSN!D12</f>
-        <v>0.12574925291786171</v>
+        <f>IUSN!E12</f>
+        <v>0.12571725548610305</v>
       </c>
       <c r="H23" s="7"/>
     </row>
@@ -2302,7 +2306,7 @@
       </c>
       <c r="C27" s="5">
         <f>C18*D5+C19*(D7+D8)+C23*D6</f>
-        <v>4.9771659506077084E-3</v>
+        <v>4.9416297308000762E-3</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
@@ -2311,7 +2315,7 @@
       </c>
       <c r="C28" s="5">
         <f>E18*D5+E19*(D7+D8)+E23*D6</f>
-        <v>4.5302796769992907E-3</v>
+        <v>4.5814807061193485E-3</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
@@ -2325,7 +2329,7 @@
       </c>
       <c r="C31" s="5">
         <f>D18*D5+D19*(D7+D8)+D23*D6</f>
-        <v>2.0028877230203581E-3</v>
+        <v>1.9830025747223454E-3</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
@@ -2334,7 +2338,7 @@
       </c>
       <c r="C32" s="5">
         <f>(F18*D5+F19*(D7+D8)+F23*D6)*2.5%</f>
-        <v>2.9664712458758679E-3</v>
+        <v>3.0011948778288109E-3</v>
       </c>
       <c r="D32" t="s">
         <v>117</v>
@@ -2346,7 +2350,7 @@
       </c>
       <c r="C33" s="6">
         <f>SUM(C31:C32)</f>
-        <v>4.9693589688962255E-3</v>
+        <v>4.9841974525511564E-3</v>
       </c>
     </row>
   </sheetData>
@@ -2357,17 +2361,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:J46"/>
+  <dimension ref="A2:Q46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
-    <col min="2" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1"/>
-    <col min="10" max="10" width="91.85546875" customWidth="1"/>
+    <col min="2" max="8" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="91.85546875" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
@@ -2378,11 +2384,12 @@
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
-      <c r="J2" s="1" t="s">
+      <c r="I2" s="9"/>
+      <c r="K2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>19</v>
       </c>
@@ -2393,11 +2400,12 @@
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
       <c r="H3" s="18"/>
-      <c r="J3" s="2" t="s">
+      <c r="I3" s="18"/>
+      <c r="K3" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="19">
         <v>2014</v>
@@ -2417,14 +2425,17 @@
       <c r="G4" s="19">
         <v>2019</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="19">
+        <v>2020</v>
+      </c>
+      <c r="I4" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>12</v>
       </c>
@@ -2446,12 +2457,15 @@
       <c r="G5" s="22">
         <v>19581640</v>
       </c>
-      <c r="H5" s="19"/>
-      <c r="J5" s="2" t="s">
+      <c r="H5" s="22">
+        <v>23478559</v>
+      </c>
+      <c r="I5" s="19"/>
+      <c r="K5" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>11</v>
       </c>
@@ -2473,12 +2487,15 @@
       <c r="G6" s="22">
         <v>34465</v>
       </c>
-      <c r="H6" s="18"/>
-      <c r="J6" s="2" t="s">
+      <c r="H6" s="22">
+        <v>45197</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="K6" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>13</v>
       </c>
@@ -2500,15 +2517,18 @@
       <c r="G7" s="23">
         <v>2E-3</v>
       </c>
-      <c r="H7" s="28">
-        <f>AVERAGE(B7:G7)</f>
-        <v>2.316666666666667E-3</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="H7" s="23">
+        <v>2E-3</v>
+      </c>
+      <c r="I7" s="28">
+        <f>AVERAGE(B7:H7)</f>
+        <v>2.2714285714285714E-3</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>16</v>
       </c>
@@ -2517,7 +2537,7 @@
         <v>862307.69230769237</v>
       </c>
       <c r="C8" s="22">
-        <f t="shared" ref="C8:G8" si="0">C6/C7</f>
+        <f t="shared" ref="C8:H8" si="0">C6/C7</f>
         <v>2675500</v>
       </c>
       <c r="D8" s="22">
@@ -2536,9 +2556,13 @@
         <f t="shared" si="0"/>
         <v>17232500</v>
       </c>
-      <c r="H8" s="28"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H8" s="22">
+        <f t="shared" si="0"/>
+        <v>22598500</v>
+      </c>
+      <c r="I8" s="28"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="20"/>
       <c r="B9" s="29"/>
       <c r="C9" s="29"/>
@@ -2546,12 +2570,13 @@
       <c r="E9" s="29"/>
       <c r="F9" s="29"/>
       <c r="G9" s="29"/>
-      <c r="H9" s="28"/>
-      <c r="J9" s="2" t="s">
+      <c r="H9" s="29"/>
+      <c r="I9" s="28"/>
+      <c r="K9" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>7</v>
       </c>
@@ -2573,12 +2598,15 @@
       <c r="G10" s="22">
         <v>435291</v>
       </c>
-      <c r="H10" s="28"/>
-      <c r="J10" s="2" t="s">
+      <c r="H10" s="22">
+        <v>497088</v>
+      </c>
+      <c r="I10" s="28"/>
+      <c r="K10" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>9</v>
       </c>
@@ -2600,9 +2628,12 @@
       <c r="G11" s="22">
         <v>51767</v>
       </c>
-      <c r="H11" s="28"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H11" s="22">
+        <v>64057</v>
+      </c>
+      <c r="I11" s="28"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>10</v>
       </c>
@@ -2611,7 +2642,7 @@
         <v>0.11564656945650684</v>
       </c>
       <c r="C12" s="24">
-        <f t="shared" ref="C12:G12" si="1">C11/C10</f>
+        <f t="shared" ref="C12:H12" si="1">C11/C10</f>
         <v>0.11443853367928221</v>
       </c>
       <c r="D12" s="24">
@@ -2630,20 +2661,24 @@
         <f t="shared" si="1"/>
         <v>0.11892504094961762</v>
       </c>
-      <c r="H12" s="28">
-        <f>AVERAGE(B12:G12)</f>
-        <v>0.11634302084452826</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="H12" s="24">
+        <f t="shared" si="1"/>
+        <v>0.1288645068881164</v>
+      </c>
+      <c r="I12" s="28">
+        <f>AVERAGE(B12:H12)</f>
+        <v>0.11813180456504087</v>
+      </c>
+      <c r="K12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>28</v>
       </c>
       <c r="B13" s="29">
-        <f t="shared" ref="B13:G13" si="2">B11/B8</f>
+        <f t="shared" ref="B13:H13" si="2">B11/B8</f>
         <v>2.9339875111507579E-3</v>
       </c>
       <c r="C13" s="29">
@@ -2666,15 +2701,19 @@
         <f t="shared" si="2"/>
         <v>3.004033077034673E-3</v>
       </c>
-      <c r="H13" s="28">
-        <f>AVERAGE(B13:G13)</f>
-        <v>2.9753339397617963E-3</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="H13" s="29">
+        <f t="shared" si="2"/>
+        <v>2.8345686660619066E-3</v>
+      </c>
+      <c r="I13" s="28">
+        <f>AVERAGE(B13:H13)</f>
+        <v>2.9552246149475263E-3</v>
+      </c>
+      <c r="K13" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>132</v>
       </c>
@@ -2687,7 +2726,7 @@
         <v>2.5785460661558589E-2</v>
       </c>
       <c r="D14" s="29">
-        <f t="shared" ref="D14:G14" si="3">D10/D8</f>
+        <f t="shared" ref="D14:H14" si="3">D10/D8</f>
         <v>2.7272017837235228E-2</v>
       </c>
       <c r="E14" s="29">
@@ -2702,12 +2741,16 @@
         <f t="shared" si="3"/>
         <v>2.5259886841723488E-2</v>
       </c>
-      <c r="H14" s="48"/>
-      <c r="J14" t="s">
+      <c r="H14" s="29">
+        <f t="shared" si="3"/>
+        <v>2.1996504192756155E-2</v>
+      </c>
+      <c r="I14" s="48"/>
+      <c r="K14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="20"/>
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
@@ -2715,9 +2758,10 @@
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
       <c r="G15" s="22"/>
-      <c r="H15" s="28"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H15" s="22"/>
+      <c r="I15" s="28"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
         <v>8</v>
       </c>
@@ -2739,17 +2783,20 @@
       <c r="G16" s="22">
         <v>5560</v>
       </c>
-      <c r="H16" s="28"/>
-      <c r="J16" t="s">
+      <c r="H16" s="22">
+        <v>6134</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="K16" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="57">
-        <f t="shared" ref="B17:G17" si="4">B16/B8</f>
+        <f t="shared" ref="B17:H17" si="4">B16/B8</f>
         <v>8.1177520071364855E-6</v>
       </c>
       <c r="C17" s="57">
@@ -2772,12 +2819,16 @@
         <f t="shared" si="4"/>
         <v>3.2264616277382854E-4</v>
       </c>
-      <c r="H17" s="28">
-        <f>AVERAGE(B17:G17)</f>
-        <v>1.893648786868177E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H17" s="57">
+        <f t="shared" si="4"/>
+        <v>2.7143394473084495E-4</v>
+      </c>
+      <c r="I17" s="28">
+        <f>AVERAGE(B17:H17)</f>
+        <v>2.0108903097882158E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>78</v>
       </c>
@@ -2802,9 +2853,12 @@
       <c r="G18" s="51">
         <v>0.12559999999999999</v>
       </c>
-      <c r="H18" s="48"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H18" s="51">
+        <v>0.1138</v>
+      </c>
+      <c r="I18" s="48"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="20"/>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -2812,9 +2866,10 @@
       <c r="E19" s="22"/>
       <c r="F19" s="22"/>
       <c r="G19" s="22"/>
-      <c r="H19" s="28"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H19" s="22"/>
+      <c r="I19" s="28"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
         <v>0</v>
       </c>
@@ -2836,14 +2891,17 @@
       <c r="G20" s="22">
         <v>2701</v>
       </c>
-      <c r="H20" s="28"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H20" s="22">
+        <v>2989</v>
+      </c>
+      <c r="I20" s="28"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>1</v>
       </c>
       <c r="B21" s="25">
-        <f t="shared" ref="B21:G21" si="5">B20/B8</f>
+        <f t="shared" ref="B21:H21" si="5">B20/B8</f>
         <v>7.0856378233719887E-4</v>
       </c>
       <c r="C21" s="25">
@@ -2866,12 +2924,16 @@
         <f t="shared" si="5"/>
         <v>1.5673872044102714E-4</v>
       </c>
-      <c r="H21" s="28">
-        <f>AVERAGE(B21:G21)</f>
-        <v>3.7287665783832907E-4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H21" s="25">
+        <f t="shared" si="5"/>
+        <v>1.3226541584618448E-4</v>
+      </c>
+      <c r="I21" s="28">
+        <f>AVERAGE(B21:H21)</f>
+        <v>3.3850362326802273E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="20"/>
       <c r="B22" s="29"/>
       <c r="C22" s="29"/>
@@ -2879,9 +2941,10 @@
       <c r="E22" s="29"/>
       <c r="F22" s="29"/>
       <c r="G22" s="29"/>
-      <c r="H22" s="28"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H22" s="29"/>
+      <c r="I22" s="28"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
         <v>77</v>
       </c>
@@ -2901,9 +2964,10 @@
       <c r="G23" s="29">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="H23" s="28"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H23" s="29"/>
+      <c r="I23" s="28"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="18"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -2911,15 +2975,16 @@
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
       <c r="G24" s="18"/>
-      <c r="H24" s="25"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H24" s="18"/>
+      <c r="I24" s="25"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>44</v>
       </c>
       <c r="B25" s="28">
-        <f>H7+H13-H17+H21</f>
-        <v>5.4755123855799743E-3</v>
+        <f>I7+I13-I17+I21</f>
+        <v>5.364067778665299E-3</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>86</v>
@@ -2929,9 +2994,11 @@
       <c r="F25" s="25"/>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
-      <c r="J25" s="8"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I25" s="25"/>
+      <c r="K25" s="8"/>
+      <c r="O25" s="7"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>45</v>
       </c>
@@ -2947,15 +3014,17 @@
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
-      <c r="J26" s="8"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I26" s="18"/>
+      <c r="K26" s="8"/>
+      <c r="O26" s="59"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="28">
         <f>B26-B25</f>
-        <v>-4.2551238557997535E-4</v>
+        <v>-3.1406777866530011E-4</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -2963,9 +3032,10 @@
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
-      <c r="J27" s="8"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I27" s="18"/>
+      <c r="K27" s="8"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
@@ -2973,37 +3043,38 @@
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
       <c r="H28" s="18"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="8"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I28" s="18"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="8"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B29" s="26">
-        <f>G7+H13-F17+G21</f>
-        <v>4.8818950303460493E-3</v>
-      </c>
-      <c r="I29" s="6"/>
-      <c r="J29" s="8"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <f>G7+I13-H17+H21</f>
+        <v>4.8160560860628652E-3</v>
+      </c>
+      <c r="J29" s="6"/>
+      <c r="K29" s="8"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B30" s="34">
         <f>B29-B25</f>
-        <v>-5.9361735523392502E-4</v>
-      </c>
-      <c r="I30" s="6"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-5.480116926024339E-4</v>
+      </c>
+      <c r="J30" s="6"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B31" s="30">
-        <f>B29-H13</f>
-        <v>1.906561090584253E-3</v>
+        <f>B29-I13</f>
+        <v>1.8608314711153389E-3</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -3011,9 +3082,12 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
-      <c r="I31" s="6"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I31" s="5"/>
+      <c r="J31" s="6"/>
+      <c r="O31" s="4"/>
+      <c r="Q31" s="60"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="12"/>
@@ -3022,15 +3096,16 @@
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
-      <c r="I32" s="6"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I32" s="5"/>
+      <c r="J32" s="6"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B33" s="12">
         <f>B26+B30</f>
-        <v>4.4563826447660739E-3</v>
+        <v>4.501988307397565E-3</v>
       </c>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -3038,9 +3113,10 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
-      <c r="I33" s="6"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I33" s="5"/>
+      <c r="J33" s="6"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="12"/>
@@ -3049,9 +3125,10 @@
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
-      <c r="I34" s="6"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I34" s="5"/>
+      <c r="J34" s="6"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>79</v>
       </c>
@@ -3069,10 +3146,11 @@
       <c r="G35" s="54">
         <v>1181</v>
       </c>
-      <c r="H35" s="5"/>
-      <c r="I35" s="6"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H35" s="54"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="6"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>80</v>
       </c>
@@ -3095,9 +3173,10 @@
         <v>6.8533294646743069E-5</v>
       </c>
       <c r="H36" s="5"/>
-      <c r="I36" s="6"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I36" s="5"/>
+      <c r="J36" s="6"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="12"/>
@@ -3106,9 +3185,10 @@
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
-      <c r="I37" s="6"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I37" s="5"/>
+      <c r="J37" s="6"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -3116,10 +3196,11 @@
       <c r="E38" s="15"/>
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="6"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H38" s="15"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="6"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="12"/>
@@ -3128,9 +3209,10 @@
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
-      <c r="I39" s="6"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I39" s="5"/>
+      <c r="J39" s="6"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="12"/>
@@ -3139,9 +3221,10 @@
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
-      <c r="I40" s="6"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I40" s="5"/>
+      <c r="J40" s="6"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="12"/>
@@ -3150,9 +3233,10 @@
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
-      <c r="I41" s="6"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I41" s="5"/>
+      <c r="J41" s="6"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="12"/>
@@ -3161,9 +3245,10 @@
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
-      <c r="I42" s="6"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I42" s="5"/>
+      <c r="J42" s="6"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="12"/>
@@ -3172,9 +3257,10 @@
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
-      <c r="I43" s="6"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I43" s="5"/>
+      <c r="J43" s="6"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="12"/>
@@ -3183,9 +3269,10 @@
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
-      <c r="I44" s="6"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I44" s="5"/>
+      <c r="J44" s="6"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="12"/>
@@ -3194,9 +3281,10 @@
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
-      <c r="I45" s="6"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I45" s="5"/>
+      <c r="J45" s="6"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="12"/>
@@ -3205,7 +3293,8 @@
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
-      <c r="I46" s="6"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3496,27 +3585,27 @@
         <v>37</v>
       </c>
       <c r="B13" s="17">
-        <f>B11/B8</f>
+        <f t="shared" ref="B13:G13" si="2">B11/B8</f>
         <v>2.1657929226736568E-3</v>
       </c>
       <c r="C13" s="17">
-        <f>C11/C8</f>
+        <f t="shared" si="2"/>
         <v>3.1293211816467632E-3</v>
       </c>
       <c r="D13" s="17">
-        <f>D11/D8</f>
+        <f t="shared" si="2"/>
         <v>3.1074074074074073E-3</v>
       </c>
       <c r="E13" s="17">
-        <f>E11/E8</f>
+        <f t="shared" si="2"/>
         <v>3.0807679200272635E-3</v>
       </c>
       <c r="F13" s="17">
-        <f>F11/F8</f>
+        <f t="shared" si="2"/>
         <v>3.8819566638178069E-3</v>
       </c>
       <c r="G13" s="17">
-        <f>G11/G8</f>
+        <f t="shared" si="2"/>
         <v>3.5845159697069475E-3</v>
       </c>
       <c r="H13" s="34">
@@ -3567,27 +3656,27 @@
         <v>21</v>
       </c>
       <c r="B16" s="17">
-        <f>B15/B8</f>
+        <f t="shared" ref="B16:G16" si="3">B15/B8</f>
         <v>9.5019659239842721E-5</v>
       </c>
       <c r="C16" s="17">
-        <f>C15/C8</f>
+        <f t="shared" si="3"/>
         <v>4.7925832809553738E-4</v>
       </c>
       <c r="D16" s="17">
-        <f>D15/D8</f>
+        <f t="shared" si="3"/>
         <v>1.5225308641975308E-3</v>
       </c>
       <c r="E16" s="17">
-        <f>E15/E8</f>
+        <f t="shared" si="3"/>
         <v>1.2987049869362718E-3</v>
       </c>
       <c r="F16" s="17">
-        <f>F15/F8</f>
+        <f t="shared" si="3"/>
         <v>1.0490171434317027E-3</v>
       </c>
       <c r="G16" s="17">
-        <f>G15/G8</f>
+        <f t="shared" si="3"/>
         <v>9.0555647020085608E-4</v>
       </c>
       <c r="H16" s="34">
@@ -3848,17 +3937,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46EB2121-1E5C-40E6-84C9-729FC25AD7CB}">
-  <dimension ref="A2:J31"/>
+  <dimension ref="A2:K31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
-    <col min="2" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1"/>
-    <col min="10" max="10" width="91.85546875" customWidth="1"/>
+    <col min="2" max="8" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="91.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>15</v>
       </c>
@@ -3869,19 +3958,20 @@
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
-      <c r="J2" s="1" t="s">
+      <c r="I2" s="9"/>
+      <c r="K2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>2014</v>
       </c>
@@ -3900,14 +3990,17 @@
       <c r="G4" s="1">
         <v>2019</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="1">
+        <v>2020</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -3929,12 +4022,15 @@
       <c r="G5" s="11">
         <v>307508</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="J5" s="2" t="s">
+      <c r="H5" s="11">
+        <v>210729</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="K5" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -3956,11 +4052,14 @@
       <c r="G6" s="11">
         <v>2713</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="H6" s="11">
+        <v>2053</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -3982,15 +4081,18 @@
       <c r="G7" s="17">
         <v>7.4000000000000003E-3</v>
       </c>
-      <c r="H7" s="7">
-        <f>AVERAGE(C7:G7)</f>
+      <c r="H7" s="17">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="I7" s="7">
+        <f>AVERAGE(C7:H7)</f>
         <v>7.4000000000000012E-3</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -3999,7 +4101,7 @@
         <v>393783.78378378379</v>
       </c>
       <c r="C8" s="11">
-        <f t="shared" ref="C8:G8" si="0">C6/C7</f>
+        <f t="shared" ref="C8:H8" si="0">C6/C7</f>
         <v>403648.64864864864</v>
       </c>
       <c r="D8" s="11">
@@ -4018,21 +4120,26 @@
         <f t="shared" si="0"/>
         <v>366621.6216216216</v>
       </c>
-      <c r="H8" s="30"/>
-      <c r="J8" s="2" t="s">
+      <c r="H8" s="11">
+        <f t="shared" si="0"/>
+        <v>277432.43243243243</v>
+      </c>
+      <c r="I8" s="30"/>
+      <c r="K8" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="30"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H9" s="1"/>
+      <c r="I9" s="30"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -4054,12 +4161,15 @@
       <c r="G10" s="11">
         <v>9792</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="J10" t="s">
+      <c r="H10" s="11">
+        <v>7586</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="K10" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -4082,17 +4192,20 @@
       <c r="G11" s="11">
         <v>2132</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="J11" t="s">
+      <c r="H11" s="11">
+        <v>1241</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="K11" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="14">
-        <f t="shared" ref="B12:G12" si="1">B11/B10</f>
+        <f t="shared" ref="B12:H12" si="1">B11/B10</f>
         <v>0.11395604395604396</v>
       </c>
       <c r="C12" s="14">
@@ -4115,15 +4228,19 @@
         <f t="shared" si="1"/>
         <v>0.21772875816993464</v>
       </c>
-      <c r="H12" s="7">
-        <f>AVERAGE(C12:G12)</f>
-        <v>0.14642301968419308</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="H12" s="14">
+        <f t="shared" si="1"/>
+        <v>0.16359082520432375</v>
+      </c>
+      <c r="I12" s="7">
+        <f>AVERAGE(C12:H12)</f>
+        <v>0.14928432060421487</v>
+      </c>
+      <c r="K12" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>28</v>
       </c>
@@ -4132,7 +4249,7 @@
         <v>2.6334248455730956E-3</v>
       </c>
       <c r="C13" s="4">
-        <f t="shared" ref="C13:G13" si="2">C11/C8</f>
+        <f t="shared" ref="C13:H13" si="2">C11/C8</f>
         <v>3.0744559758955473E-3</v>
       </c>
       <c r="D13" s="4">
@@ -4151,15 +4268,19 @@
         <f t="shared" si="2"/>
         <v>5.8152598599336535E-3</v>
       </c>
-      <c r="H13" s="7">
-        <f>AVERAGE(C13:G13)</f>
-        <v>3.5453259492307376E-3</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="H13" s="4">
+        <f t="shared" si="2"/>
+        <v>4.4731612274719924E-3</v>
+      </c>
+      <c r="I13" s="7">
+        <f>AVERAGE(C13:H13)</f>
+        <v>3.6999651622709466E-3</v>
+      </c>
+      <c r="K13" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -4167,9 +4288,10 @@
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H14" s="11"/>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
@@ -4191,12 +4313,15 @@
       <c r="G15" s="11">
         <v>2187</v>
       </c>
-      <c r="H15" s="7"/>
-      <c r="J15" t="s">
+      <c r="H15" s="11">
+        <v>1175</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="K15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -4209,7 +4334,7 @@
         <v>3.2701707398727822E-3</v>
       </c>
       <c r="D16" s="17">
-        <f t="shared" ref="D16:G16" si="3">D15/D8</f>
+        <f t="shared" ref="D16:H16" si="3">D15/D8</f>
         <v>4.9717587939698488E-3</v>
       </c>
       <c r="E16" s="17">
@@ -4224,12 +4349,16 @@
         <f t="shared" si="3"/>
         <v>5.9652782897161817E-3</v>
       </c>
-      <c r="H16" s="7">
-        <f>AVERAGE(C16:G16)</f>
-        <v>4.8498234918020891E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H16" s="17">
+        <f t="shared" si="3"/>
+        <v>4.2352654651729178E-3</v>
+      </c>
+      <c r="I16" s="7">
+        <f>AVERAGE(C16:H16)</f>
+        <v>4.7473971540305604E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>78</v>
       </c>
@@ -4254,9 +4383,12 @@
       <c r="G17" s="31">
         <v>0.21609999999999999</v>
       </c>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H17" s="31">
+        <v>0.11650000000000001</v>
+      </c>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -4264,9 +4396,10 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H18" s="11"/>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>0</v>
       </c>
@@ -4288,9 +4421,12 @@
       <c r="G19" s="11">
         <v>466</v>
       </c>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H19" s="11">
+        <v>309</v>
+      </c>
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
@@ -4299,7 +4435,7 @@
         <v>1.5795470144131778E-3</v>
       </c>
       <c r="C20" s="4">
-        <f t="shared" ref="C20:G20" si="4">C19/C8</f>
+        <f t="shared" ref="C20:H20" si="4">C19/C8</f>
         <v>1.7639102778707733E-3</v>
       </c>
       <c r="D20" s="4">
@@ -4318,17 +4454,21 @@
         <f t="shared" si="4"/>
         <v>1.2710652414301513E-3</v>
       </c>
-      <c r="H20" s="7">
-        <f>AVERAGE(C20:G20)</f>
-        <v>1.3558730194178812E-3</v>
-      </c>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H21" s="5"/>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H20" s="4">
+        <f t="shared" si="4"/>
+        <v>1.1137847053093034E-3</v>
+      </c>
+      <c r="I20" s="7">
+        <f>AVERAGE(C20:H20)</f>
+        <v>1.3155249670664514E-3</v>
+      </c>
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I21" s="5"/>
+      <c r="K21" s="8"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>77</v>
       </c>
@@ -4348,10 +4488,11 @@
       <c r="G22" s="29">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="H22" s="5"/>
-      <c r="J22" s="8"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H22" s="29"/>
+      <c r="I22" s="5"/>
+      <c r="K22" s="8"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -4360,21 +4501,22 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
-      <c r="J23" s="8"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I23" s="5"/>
+      <c r="K23" s="8"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>44</v>
       </c>
       <c r="B24" s="28">
-        <f>H7+H13-H16+H20</f>
-        <v>7.4513754768465298E-3</v>
+        <f>I7+I13-I16+I20</f>
+        <v>7.6680929753068392E-3</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>45</v>
       </c>
@@ -4386,47 +4528,47 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="28">
         <f>B25-B24</f>
-        <v>-2.1913754768465386E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-2.408092975306848E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="18"/>
       <c r="B27" s="18"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B28" s="30">
-        <f>G7+AVERAGE(B13:G13)+G20-AVERAGE(D16:G16)</f>
-        <v>6.8196709936002003E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <f>H7+AVERAGE(B13:H13)+H20-AVERAGE(D16:H16)</f>
+        <v>7.0185445283327264E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B29" s="7">
         <f>B28-B24</f>
-        <v>-6.3170448324632953E-4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-6.495484469741129E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B31" s="30">
         <f>B25+B29</f>
-        <v>4.6282955167536617E-3</v>
+        <v>4.6104515530258783E-3</v>
       </c>
     </row>
   </sheetData>
@@ -4436,50 +4578,54 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3319A48F-C74C-4C2A-9714-F1A50A94B19B}">
-  <dimension ref="A2:F36"/>
+  <dimension ref="A2:G36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.28515625" customWidth="1"/>
-    <col min="2" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="91.85546875" customWidth="1"/>
+    <col min="2" max="4" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="91.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="9"/>
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>2018</v>
       </c>
       <c r="C4" s="1">
         <v>2019</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -4489,12 +4635,15 @@
       <c r="C5" s="11">
         <v>861947</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="F5" s="2" t="s">
+      <c r="D5" s="11">
+        <v>1103291</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="G5" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -4504,9 +4653,12 @@
       <c r="C6" s="11">
         <v>1886</v>
       </c>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="11">
+        <v>3207</v>
+      </c>
+      <c r="G6" s="8"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -4516,36 +4668,44 @@
       <c r="C7" s="17">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="D7" s="7">
-        <f>AVERAGE(B7:C7)</f>
+      <c r="D7" s="17">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="F7" t="s">
+      <c r="E7" s="7">
+        <f>AVERAGE(B7:D7)</f>
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="G7" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="11">
-        <f t="shared" ref="B8:C8" si="0">B6/B7</f>
+        <f t="shared" ref="B8:D8" si="0">B6/B7</f>
         <v>76285.71428571429</v>
       </c>
       <c r="C8" s="11">
         <f t="shared" si="0"/>
         <v>538857.14285714284</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="11">
+        <f t="shared" si="0"/>
+        <v>916285.71428571432</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="G8" s="8"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E9" s="1"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -4555,9 +4715,12 @@
       <c r="C10" s="11">
         <v>12293</v>
       </c>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="61">
+        <v>17604</v>
+      </c>
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -4567,25 +4730,32 @@
       <c r="C11" s="11">
         <v>1482</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D11" s="11">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="14">
-        <f t="shared" ref="B12:C12" si="1">B11/B10</f>
+        <f t="shared" ref="B12:D12" si="1">B11/B10</f>
         <v>0.13094209161624892</v>
       </c>
       <c r="C12" s="14">
         <f t="shared" si="1"/>
         <v>0.12055641421947449</v>
       </c>
-      <c r="D12" s="27">
-        <f>AVERAGE(B12:C12)</f>
-        <v>0.12574925291786171</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D12" s="14">
+        <f t="shared" si="1"/>
+        <v>0.12565326062258578</v>
+      </c>
+      <c r="E12" s="27">
+        <f>AVERAGE(B12:D12)</f>
+        <v>0.12571725548610305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
@@ -4597,17 +4767,22 @@
         <f>C11/C8</f>
         <v>2.7502651113467656E-3</v>
       </c>
-      <c r="D13" s="7">
-        <f>AVERAGE(B13:C13)</f>
-        <v>3.361087611853158E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D13" s="4">
+        <f>D11/D8</f>
+        <v>2.4140941690053009E-3</v>
+      </c>
+      <c r="E13" s="7">
+        <f>AVERAGE(B13:D13)</f>
+        <v>3.0454231309038726E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
@@ -4617,8 +4792,11 @@
       <c r="C15" s="11">
         <v>250</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D15" s="11">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -4630,12 +4808,16 @@
         <f>C15/C8</f>
         <v>4.6394485683987275E-4</v>
       </c>
-      <c r="D16" s="7">
-        <f>AVERAGE(B16:C16)</f>
-        <v>2.5163534976825098E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D16" s="17">
+        <f>D15/D8</f>
+        <v>8.2507015902712818E-4</v>
+      </c>
+      <c r="E16" s="7">
+        <f>AVERAGE(B16:D16)</f>
+        <v>4.4278028618787677E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>78</v>
       </c>
@@ -4645,14 +4827,18 @@
       <c r="C17" s="31">
         <v>0.1915</v>
       </c>
-      <c r="D17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D17" s="31">
+        <v>0.1986</v>
+      </c>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D18" s="11"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>0</v>
       </c>
@@ -4662,8 +4848,11 @@
       <c r="C19" s="11">
         <v>271</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D19" s="11">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
@@ -4675,17 +4864,21 @@
         <f>C19/C8</f>
         <v>5.0291622481442202E-4</v>
       </c>
-      <c r="D20" s="6">
-        <f>AVERAGE(B20:C20)</f>
-        <v>1.4771135431188216E-3</v>
-      </c>
-      <c r="F20" s="8"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D21" s="5"/>
-      <c r="F21" s="8"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D20" s="4">
+        <f>D19/D8</f>
+        <v>5.8169628936700966E-4</v>
+      </c>
+      <c r="E20" s="6">
+        <f>AVERAGE(B20:D20)</f>
+        <v>1.178641125201551E-3</v>
+      </c>
+      <c r="G20" s="8"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E21" s="5"/>
+      <c r="G21" s="8"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>77</v>
       </c>
@@ -4695,115 +4888,126 @@
       <c r="C22" s="7">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="F22" s="8"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D22" s="7"/>
+      <c r="E22" s="5"/>
+      <c r="G22" s="8"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
-      <c r="F23" s="8"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E23" s="5"/>
+      <c r="G23" s="8"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>43</v>
       </c>
       <c r="B24" s="6">
-        <f>D7+D13-D16+D20</f>
-        <v>8.0865658052037288E-3</v>
+        <f>E7+E13-E16+E20</f>
+        <v>7.2812839699175468E-3</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
-      <c r="F24" s="8"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E24" s="5"/>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="18"/>
-      <c r="F25" s="8"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25" s="8"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="8"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E27" s="6"/>
-      <c r="F27" s="8"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F26" s="6"/>
+      <c r="G26" s="8"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F27" s="6"/>
+      <c r="G27" s="8"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B28" s="15">
-        <f>D7+C13-C16+C20</f>
-        <v>6.2892364793213154E-3</v>
-      </c>
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <f>E7+E13-AVERAGE(C16:D16)+AVERAGE(C20:D20)</f>
+        <v>6.4432218800610881E-3</v>
+      </c>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B29" s="4">
         <f>B28-C13</f>
-        <v>3.5389713679745498E-3</v>
+        <v>3.6929567687143225E-3</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="6"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E29" s="5"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="6"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E30" s="5"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B31" s="15">
         <f>B28-0.05%</f>
-        <v>5.789236479321315E-3</v>
+        <v>5.9432218800610885E-3</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="6"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E31" s="5"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="6"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E32" s="5"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="6"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E33" s="5"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
-      <c r="E34" s="6"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E34" s="5"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="6"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E35" s="5"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
-      <c r="E36" s="6"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5437,17 +5641,17 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4E9972-EF6D-435D-B893-B5209367B0F1}">
-  <dimension ref="A2:J31"/>
+  <dimension ref="A2:K31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
-    <col min="2" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1"/>
-    <col min="10" max="10" width="91.85546875" customWidth="1"/>
+    <col min="2" max="8" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="91.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>103</v>
       </c>
@@ -5458,19 +5662,20 @@
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
-      <c r="J2" s="1" t="s">
+      <c r="I2" s="9"/>
+      <c r="K2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>2014</v>
       </c>
@@ -5489,11 +5694,14 @@
       <c r="G4" s="1">
         <v>2019</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="1">
+        <v>2020</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -5515,10 +5723,13 @@
       <c r="G5" s="11">
         <v>736031</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H5" s="11">
+        <v>629077</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -5540,11 +5751,14 @@
       <c r="G6" s="11">
         <v>4948</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="H6" s="11">
+        <v>3674</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -5566,13 +5780,16 @@
       <c r="G7" s="17">
         <v>6.7999999999999996E-3</v>
       </c>
-      <c r="H7" s="7">
-        <f>AVERAGE(C7:G7)</f>
-        <v>6.7999999999999988E-3</v>
-      </c>
-      <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H7" s="17">
+        <v>1.8E-3</v>
+      </c>
+      <c r="I7" s="7">
+        <f>AVERAGE(C7:H7)</f>
+        <v>5.9666666666666661E-3</v>
+      </c>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -5581,7 +5798,7 @@
         <v>329714.28571428568</v>
       </c>
       <c r="C8" s="11">
-        <f t="shared" ref="C8:G8" si="0">C6/C7</f>
+        <f t="shared" ref="C8:H8" si="0">C6/C7</f>
         <v>350294.11764705885</v>
       </c>
       <c r="D8" s="11">
@@ -5600,21 +5817,26 @@
         <f t="shared" si="0"/>
         <v>727647.0588235294</v>
       </c>
-      <c r="H8" s="30"/>
-      <c r="J8" t="s">
+      <c r="H8" s="11">
+        <f>(G5+H5)/2</f>
+        <v>682554</v>
+      </c>
+      <c r="I8" s="30"/>
+      <c r="K8" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="30"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H9" s="1"/>
+      <c r="I9" s="30"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -5636,9 +5858,12 @@
       <c r="G10" s="11">
         <v>22036</v>
       </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H10" s="11">
+        <v>16847</v>
+      </c>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -5660,14 +5885,17 @@
       <c r="G11" s="11">
         <v>3336</v>
       </c>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H11" s="11">
+        <v>2435</v>
+      </c>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="14">
-        <f t="shared" ref="B12:G12" si="1">B11/B10</f>
+        <f t="shared" ref="B12:H12" si="1">B11/B10</f>
         <v>0.11126727570859686</v>
       </c>
       <c r="C12" s="14">
@@ -5690,12 +5918,16 @@
         <f t="shared" si="1"/>
         <v>0.15138863677618442</v>
       </c>
-      <c r="H12" s="7">
-        <f>AVERAGE(C12:G12)</f>
-        <v>0.12818992219549338</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H12" s="14">
+        <f t="shared" si="1"/>
+        <v>0.1445361191903603</v>
+      </c>
+      <c r="I12" s="7">
+        <f>AVERAGE(C12:H12)</f>
+        <v>0.13091428836130456</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>28</v>
       </c>
@@ -5704,7 +5936,7 @@
         <v>2.8812824956672449E-3</v>
       </c>
       <c r="C13" s="4">
-        <f t="shared" ref="C13:G13" si="2">C11/C8</f>
+        <f t="shared" ref="C13:H13" si="2">C11/C8</f>
         <v>3.2372795969773296E-3</v>
       </c>
       <c r="D13" s="4">
@@ -5723,12 +5955,16 @@
         <f t="shared" si="2"/>
         <v>4.58464025869038E-3</v>
       </c>
-      <c r="H13" s="7">
-        <f>AVERAGE(C13:G13)</f>
-        <v>3.6849452862168881E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H13" s="4">
+        <f t="shared" si="2"/>
+        <v>3.5674833053501993E-3</v>
+      </c>
+      <c r="I13" s="7">
+        <f>AVERAGE(C13:H13)</f>
+        <v>3.6653682894057737E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -5736,9 +5972,10 @@
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H14" s="11"/>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
@@ -5760,9 +5997,12 @@
       <c r="G15" s="11">
         <v>335</v>
       </c>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H15" s="11">
+        <v>270</v>
+      </c>
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -5775,7 +6015,7 @@
         <v>4.9101595298068842E-4</v>
       </c>
       <c r="D16" s="17">
-        <f t="shared" ref="D16:G16" si="3">D15/D8</f>
+        <f t="shared" ref="D16:H16" si="3">D15/D8</f>
         <v>6.0245051837888781E-4</v>
       </c>
       <c r="E16" s="17">
@@ -5790,12 +6030,16 @@
         <f t="shared" si="3"/>
         <v>4.6038803556992726E-4</v>
       </c>
-      <c r="H16" s="7">
-        <f>AVERAGE(C16:G16)</f>
-        <v>4.9014536569380227E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H16" s="17">
+        <f t="shared" si="3"/>
+        <v>3.9557309751316381E-4</v>
+      </c>
+      <c r="I16" s="7">
+        <f>AVERAGE(C16:H16)</f>
+        <v>4.7438332099702924E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>78</v>
       </c>
@@ -5820,9 +6064,12 @@
       <c r="G17" s="31">
         <v>6.8599999999999994E-2</v>
       </c>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H17" s="31">
+        <v>0.19939999999999999</v>
+      </c>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -5830,9 +6077,10 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H18" s="11"/>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>0</v>
       </c>
@@ -5854,9 +6102,12 @@
       <c r="G19" s="11">
         <v>686</v>
       </c>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H19" s="11">
+        <v>366</v>
+      </c>
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
@@ -5865,7 +6116,7 @@
         <v>8.3708838821490471E-4</v>
       </c>
       <c r="C20" s="4">
-        <f t="shared" ref="C20:G20" si="4">C19/C8</f>
+        <f t="shared" ref="C20:H20" si="4">C19/C8</f>
         <v>4.282115869017632E-4</v>
       </c>
       <c r="D20" s="4">
@@ -5884,17 +6135,21 @@
         <f t="shared" si="4"/>
         <v>9.4276475343573168E-4</v>
       </c>
-      <c r="H20" s="7">
-        <f>AVERAGE(C20:G20)</f>
-        <v>9.1731561021324705E-4</v>
-      </c>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H21" s="5"/>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H20" s="4">
+        <f t="shared" si="4"/>
+        <v>5.3622130996228872E-4</v>
+      </c>
+      <c r="I20" s="7">
+        <f>AVERAGE(C20:H20)</f>
+        <v>8.5379989350475394E-4</v>
+      </c>
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I21" s="5"/>
+      <c r="K21" s="8"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>77</v>
       </c>
@@ -5914,10 +6169,11 @@
       <c r="G22" s="29">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="H22" s="5"/>
-      <c r="J22" s="8"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H22" s="29"/>
+      <c r="I22" s="5"/>
+      <c r="K22" s="8"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -5926,21 +6182,22 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
-      <c r="J23" s="8"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I23" s="5"/>
+      <c r="K23" s="8"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>44</v>
       </c>
       <c r="B24" s="28">
-        <f>H7+H13-H16+H20</f>
-        <v>1.091211553073633E-2</v>
+        <f>I7+I13-I16+I20</f>
+        <v>1.0011451528580163E-2</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>45</v>
       </c>
@@ -5952,47 +6209,47 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="28">
         <f>B25-B24</f>
-        <v>-6.5211553073633854E-4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2.48548471419828E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="18"/>
       <c r="B27" s="18"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B28" s="30">
-        <f>0.18%+AVERAGE(B13:G13)+AVERAGE(F20:G20)-AVERAGE(F16:G16)</f>
-        <v>5.7099486057513279E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <f>0.18%+AVERAGE(B13:H13)+AVERAGE(F20:H20)-AVERAGE(F16:H16)</f>
+        <v>5.6395368492800409E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B29" s="7">
         <f>B28-B24</f>
-        <v>-5.202166924985002E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-4.3719146793001224E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B31" s="30">
         <f>B25+B29</f>
-        <v>5.0578330750149893E-3</v>
+        <v>5.8880853206998689E-3</v>
       </c>
     </row>
   </sheetData>

--- a/iShares/iShares-KostenBepaling2020.xlsx
+++ b/iShares/iShares-KostenBepaling2020.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsen/KeuzeWelkIndexFonds/OnderzoekPerFonds/iShares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{A6ACE176-4C08-4AFF-ACEF-0847542540D3}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{37CF9434-8F84-4266-A9E4-E879F436B0AF}"/>
+  <xr:revisionPtr revIDLastSave="136" documentId="13_ncr:1_{A6ACE176-4C08-4AFF-ACEF-0847542540D3}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{18215C9B-3CA9-437E-AFD9-892323CF4419}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
     <author>Gerben</author>
   </authors>
   <commentList>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{BC3B4BF2-0E46-4EF7-A78C-8FC9B39EDDF8}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{BC3B4BF2-0E46-4EF7-A78C-8FC9B39EDDF8}">
       <text>
         <r>
           <rPr>
@@ -89,7 +89,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{4A660686-6E86-4023-9ACD-41E13C92ACF2}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{4A660686-6E86-4023-9ACD-41E13C92ACF2}">
       <text>
         <r>
           <rPr>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="134">
   <si>
     <t>Transaction costs</t>
   </si>
@@ -309,9 +309,6 @@
     <t>Gemiddeld vermogen via TER (operation expense) teruggerekend</t>
   </si>
   <si>
-    <t>4 basispunten er naast maar, niet onaardig</t>
-  </si>
-  <si>
     <t>6 basispunten er naast maar, niet onaardig</t>
   </si>
   <si>
@@ -321,9 +318,6 @@
     <t>wel gek dat ik meer kosten vind als de tracking difference</t>
   </si>
   <si>
-    <t>Tracking diff toekomst</t>
-  </si>
-  <si>
     <t>MSCI ACWI IMI</t>
   </si>
   <si>
@@ -348,21 +342,12 @@
     <t>World + Emerging</t>
   </si>
   <si>
-    <t>Verschil kosten toekomst en verleden</t>
-  </si>
-  <si>
     <t>Derivatives</t>
   </si>
   <si>
     <t>Securities on loan</t>
   </si>
   <si>
-    <t>Interest income</t>
-  </si>
-  <si>
-    <t>% interest income</t>
-  </si>
-  <si>
     <t>Rente inkomsten zijn voor IWDA en EMIM tijdens 2016-2019 meestal hoger dan de kosten</t>
   </si>
   <si>
@@ -399,9 +384,6 @@
     <t>Vermogen loopt wat terug. Wel nog boven de 200 miljoen grens.</t>
   </si>
   <si>
-    <t>Gok TD toekomst</t>
-  </si>
-  <si>
     <t>Kosten</t>
   </si>
   <si>
@@ -532,6 +514,12 @@
   </si>
   <si>
     <t>2015-2020</t>
+  </si>
+  <si>
+    <t>2014-2020</t>
+  </si>
+  <si>
+    <t>3 basispunten er naast maar, niet onaardig</t>
   </si>
 </sst>
 </file>
@@ -545,7 +533,7 @@
     <numFmt numFmtId="165" formatCode="0.000%"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ [$€-413]\ * #,##0_ ;_ [$€-413]\ * \-#,##0_ ;_ [$€-413]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="_ [$€-413]\ * #,##0_ ;_ [$€-413]\ * \-#,##0_ ;_ [$€-413]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -661,7 +649,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -724,16 +712,13 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1078,12 +1063,12 @@
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1093,15 +1078,15 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045330D2-0890-4532-8ABA-CDB206A2E066}">
-  <dimension ref="B1:N47"/>
+  <dimension ref="B1:O47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="44.140625" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" customWidth="1"/>
-    <col min="14" max="14" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C1" s="46">
         <v>2013</v>
       </c>
@@ -1123,18 +1108,21 @@
       <c r="I1" s="46">
         <v>2019</v>
       </c>
-      <c r="J1" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="K1" s="37"/>
-      <c r="L1" s="35" t="s">
+      <c r="J1" s="46">
+        <v>2020</v>
+      </c>
+      <c r="K1" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="L1" s="37"/>
+      <c r="M1" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="M1" s="35" t="s">
+      <c r="N1" s="35" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="35" t="s">
         <v>47</v>
       </c>
@@ -1157,15 +1145,16 @@
       <c r="I2" s="36">
         <v>27.76</v>
       </c>
-      <c r="J2" s="38">
+      <c r="J2" s="36"/>
+      <c r="K2" s="38">
         <f>AVERAGE(D2:I2)</f>
         <v>8.9283333333333346</v>
       </c>
-      <c r="K2" s="37"/>
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N2" s="37"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="35" t="s">
         <v>48</v>
       </c>
@@ -1188,12 +1177,13 @@
       <c r="I3" s="36">
         <v>28.4</v>
       </c>
-      <c r="J3" s="37"/>
+      <c r="J3" s="36"/>
       <c r="K3" s="37"/>
-      <c r="L3" s="38"/>
+      <c r="L3" s="37"/>
       <c r="M3" s="38"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N3" s="38"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="35" t="s">
         <v>49</v>
       </c>
@@ -1216,12 +1206,13 @@
       <c r="I4" s="39">
         <v>27.67</v>
       </c>
-      <c r="J4" s="37"/>
+      <c r="J4" s="39"/>
       <c r="K4" s="37"/>
-      <c r="L4" s="38"/>
+      <c r="L4" s="37"/>
       <c r="M4" s="38"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N4" s="38"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="35" t="s">
         <v>50</v>
       </c>
@@ -1250,15 +1241,16 @@
         <f t="shared" si="0"/>
         <v>0.63999999999999702</v>
       </c>
-      <c r="J5" s="37"/>
+      <c r="J5" s="36"/>
       <c r="K5" s="37"/>
-      <c r="L5" s="38">
+      <c r="L5" s="37"/>
+      <c r="M5" s="38">
         <f>AVERAGE(D5:I5)</f>
         <v>0.50499999999999989</v>
       </c>
-      <c r="M5" s="38"/>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N5" s="38"/>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="35" t="s">
         <v>51</v>
       </c>
@@ -1287,21 +1279,22 @@
         <f t="shared" si="1"/>
         <v>8.9999999999999858E-2</v>
       </c>
-      <c r="J6" s="37"/>
+      <c r="J6" s="36"/>
       <c r="K6" s="37"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38">
+      <c r="L6" s="37"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38">
         <f>AVERAGE(D6:I6)</f>
         <v>0.10500000000000019</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J7" s="37"/>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J8" s="37"/>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K7" s="37"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K8" s="37"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="40" t="s">
         <v>52</v>
       </c>
@@ -1321,14 +1314,15 @@
       <c r="I9" s="41">
         <v>17.45</v>
       </c>
-      <c r="J9" s="38">
-        <f t="shared" ref="J9:J22" si="2">AVERAGE(D9:I9)</f>
+      <c r="J9" s="41"/>
+      <c r="K9" s="38">
+        <f t="shared" ref="K9:K22" si="2">AVERAGE(D9:I9)</f>
         <v>6.9659999999999993</v>
       </c>
-      <c r="K9" s="42"/>
       <c r="L9" s="42"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M9" s="42"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="40" t="s">
         <v>53</v>
       </c>
@@ -1348,11 +1342,12 @@
       <c r="I10" s="43">
         <v>18.100000000000001</v>
       </c>
-      <c r="J10" s="37"/>
-      <c r="K10" s="42"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="37"/>
       <c r="L10" s="42"/>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M10" s="42"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="40" t="s">
         <v>54</v>
       </c>
@@ -1372,11 +1367,11 @@
       <c r="I11">
         <v>17.64</v>
       </c>
-      <c r="J11" s="37"/>
-      <c r="K11" s="42"/>
+      <c r="K11" s="37"/>
       <c r="L11" s="42"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M11" s="42"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="40" t="s">
         <v>50</v>
       </c>
@@ -1401,14 +1396,15 @@
         <f>I10-I9</f>
         <v>0.65000000000000213</v>
       </c>
-      <c r="J12" s="37"/>
-      <c r="L12" s="44">
+      <c r="J12" s="41"/>
+      <c r="K12" s="37"/>
+      <c r="M12" s="44">
         <f>AVERAGE(E12:I12)</f>
         <v>0.51800000000000135</v>
       </c>
-      <c r="M12" s="42"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N12" s="42"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="40" t="s">
         <v>51</v>
       </c>
@@ -1433,20 +1429,21 @@
         <f t="shared" si="3"/>
         <v>-0.19000000000000128</v>
       </c>
-      <c r="J13" s="37"/>
-      <c r="L13" s="44"/>
-      <c r="M13" s="44">
+      <c r="J13" s="41"/>
+      <c r="K13" s="37"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="44">
         <f>AVERAGE(E13:I13)</f>
         <v>-0.12800000000000117</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J14" s="37"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J15" s="37"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K14" s="37"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K15" s="37"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="45" t="s">
         <v>57</v>
       </c>
@@ -1459,13 +1456,14 @@
       <c r="I16" s="42">
         <v>25.73</v>
       </c>
-      <c r="J16" s="37"/>
-      <c r="K16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="37"/>
       <c r="L16" s="42"/>
       <c r="M16" s="42"/>
       <c r="N16" s="42"/>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O16" s="42"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="40" t="s">
         <v>56</v>
       </c>
@@ -1478,13 +1476,14 @@
       <c r="I17" s="42">
         <v>26.78</v>
       </c>
-      <c r="J17" s="37"/>
-      <c r="K17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="37"/>
       <c r="L17" s="42"/>
       <c r="M17" s="42"/>
       <c r="N17" s="42"/>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O17" s="42"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="40" t="s">
         <v>55</v>
       </c>
@@ -1497,13 +1496,14 @@
       <c r="I18" s="42">
         <v>26.19</v>
       </c>
-      <c r="J18" s="37"/>
-      <c r="K18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="37"/>
       <c r="L18" s="42"/>
       <c r="M18" s="42"/>
       <c r="N18" s="42"/>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O18" s="42"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="40" t="s">
         <v>50</v>
       </c>
@@ -1517,26 +1517,27 @@
         <f>I17-I16</f>
         <v>1.0500000000000007</v>
       </c>
-      <c r="J19" s="37"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42">
+      <c r="J19" s="42"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42">
         <f>AVERAGE(I19)</f>
         <v>1.0500000000000007</v>
       </c>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42" t="s">
+      <c r="N19" s="42"/>
+      <c r="O19" s="42" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J20" s="37"/>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J21" s="37"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K20" s="37"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K21" s="37"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" s="35" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E22">
         <v>-7.43</v>
@@ -1553,12 +1554,12 @@
       <c r="I22">
         <v>11.06</v>
       </c>
-      <c r="J22" s="37">
+      <c r="K22" s="37">
         <f t="shared" si="2"/>
         <v>4.24</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" s="40" t="s">
         <v>56</v>
       </c>
@@ -1577,9 +1578,9 @@
       <c r="I23">
         <v>11.5</v>
       </c>
-      <c r="J23" s="37"/>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="K23" s="37"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="40" t="s">
         <v>55</v>
       </c>
@@ -1598,9 +1599,9 @@
       <c r="I24">
         <v>11.92</v>
       </c>
-      <c r="J24" s="37"/>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="K24" s="37"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="35" t="s">
         <v>50</v>
       </c>
@@ -1624,13 +1625,13 @@
         <f>I24-I22</f>
         <v>0.85999999999999943</v>
       </c>
-      <c r="J25" s="37"/>
-      <c r="L25" s="55">
+      <c r="K25" s="37"/>
+      <c r="M25" s="52">
         <f>AVERAGE(E25:I25)</f>
         <v>0.52599999999999913</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="35" t="s">
         <v>51</v>
       </c>
@@ -1654,15 +1655,15 @@
         <f>I22-I23</f>
         <v>-0.4399999999999995</v>
       </c>
-      <c r="J26" s="37"/>
-      <c r="M26" s="55">
+      <c r="K26" s="37"/>
+      <c r="N26" s="52">
         <f>AVERAGE(E26:I26)</f>
         <v>-0.19600000000000026</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" s="35" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E29">
         <v>-15.34</v>
@@ -1679,12 +1680,12 @@
       <c r="I29">
         <v>17.47</v>
       </c>
-      <c r="J29" s="55">
+      <c r="K29" s="52">
         <f>AVERAGE(E29:I29)</f>
         <v>6.806</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B30" s="40" t="s">
         <v>56</v>
       </c>
@@ -1704,7 +1705,7 @@
         <v>18.420000000000002</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" s="40" t="s">
         <v>55</v>
       </c>
@@ -1724,7 +1725,7 @@
         <v>18.88</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="35" t="s">
         <v>50</v>
       </c>
@@ -1748,12 +1749,12 @@
         <f>I31-I29</f>
         <v>1.4100000000000001</v>
       </c>
-      <c r="L32" s="55">
+      <c r="M32" s="52">
         <f>AVERAGE(E32:I32)</f>
         <v>1.0720000000000003</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="35" t="s">
         <v>51</v>
       </c>
@@ -1777,23 +1778,23 @@
         <f>I29-I30</f>
         <v>-0.95000000000000284</v>
       </c>
-      <c r="L33" s="55"/>
-      <c r="M33" s="55">
+      <c r="M33" s="52"/>
+      <c r="N33" s="52">
         <f>AVERAGE(E33:I33)</f>
         <v>-0.67400000000000093</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L34" s="55"/>
-      <c r="M34" s="55"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L35" s="55"/>
-      <c r="M35" s="55"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M34" s="52"/>
+      <c r="N34" s="52"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B36" s="35" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E36">
         <v>-15.33</v>
@@ -1810,10 +1811,10 @@
       <c r="I36">
         <v>17.54</v>
       </c>
-      <c r="L36" s="55"/>
-      <c r="M36" s="55"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M36" s="52"/>
+      <c r="N36" s="52"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B37" s="40" t="s">
         <v>56</v>
       </c>
@@ -1832,10 +1833,10 @@
       <c r="I37">
         <v>18.88</v>
       </c>
-      <c r="L37" s="55"/>
-      <c r="M37" s="55"/>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M37" s="52"/>
+      <c r="N37" s="52"/>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B38" s="40" t="s">
         <v>55</v>
       </c>
@@ -1854,10 +1855,10 @@
       <c r="I38">
         <v>18.420000000000002</v>
       </c>
-      <c r="L38" s="55"/>
-      <c r="M38" s="55"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M38" s="52"/>
+      <c r="N38" s="52"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B39" s="35" t="s">
         <v>50</v>
       </c>
@@ -1881,13 +1882,13 @@
         <f t="shared" si="4"/>
         <v>1.3399999999999999</v>
       </c>
-      <c r="L39" s="55">
-        <f t="shared" ref="L39" si="5">AVERAGE(E39:I39)</f>
+      <c r="M39" s="52">
+        <f t="shared" ref="M39" si="5">AVERAGE(E39:I39)</f>
         <v>1.0259999999999991</v>
       </c>
-      <c r="M39" s="55"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N39" s="52"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" s="35" t="s">
         <v>51</v>
       </c>
@@ -1911,14 +1912,14 @@
         <f t="shared" si="6"/>
         <v>-0.88000000000000256</v>
       </c>
-      <c r="M40" s="55">
-        <f t="shared" ref="M40" si="7">AVERAGE(E40:I40)</f>
+      <c r="N40" s="52">
+        <f t="shared" ref="N40" si="7">AVERAGE(E40:I40)</f>
         <v>-0.62799999999999978</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B43" s="35" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E43">
         <v>-3.27</v>
@@ -1936,9 +1937,9 @@
         <v>19.13</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B44" s="35" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E44">
         <v>-2.73</v>
@@ -1956,9 +1957,9 @@
         <v>19.84</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B45" s="35" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E45">
         <v>-3.28</v>
@@ -1976,7 +1977,7 @@
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B46" s="35" t="s">
         <v>50</v>
       </c>
@@ -2000,12 +2001,12 @@
         <f t="shared" si="8"/>
         <v>0.71000000000000085</v>
       </c>
-      <c r="L46" s="55">
+      <c r="M46" s="52">
         <f>AVERAGE(F46:I46)</f>
         <v>0.66249999999999964</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B47" s="35" t="s">
         <v>51</v>
       </c>
@@ -2029,7 +2030,7 @@
         <f t="shared" si="9"/>
         <v>-0.14000000000000057</v>
       </c>
-      <c r="M47">
+      <c r="N47">
         <f>SUM(F47:I47)</f>
         <v>-0.19000000000000128</v>
       </c>
@@ -2053,7 +2054,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C2" s="49">
         <v>53732257.130000003</v>
@@ -2063,17 +2064,17 @@
       <c r="C3" s="49"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C4" s="56" t="s">
-        <v>133</v>
+      <c r="C4" s="53" t="s">
+        <v>127</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C5" s="49">
         <v>41819772.990000002</v>
@@ -2085,7 +2086,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C6" s="49">
         <v>5480574.1299999999</v>
@@ -2097,7 +2098,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C7" s="49">
         <v>5789028.6699999999</v>
@@ -2109,7 +2110,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" s="49">
         <v>642881.34999999963</v>
@@ -2121,7 +2122,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C9" s="49">
         <v>53732257.140000008</v>
@@ -2132,7 +2133,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C11" s="49">
         <v>53089375.780000001</v>
@@ -2141,7 +2142,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" s="49">
         <v>47608801.660000004</v>
@@ -2159,37 +2160,37 @@
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C18" s="7">
         <f>IWDA!B29</f>
         <v>4.8160560860628652E-3</v>
       </c>
       <c r="D18" s="7">
-        <f>IWDA!B31</f>
+        <f>IWDA!B30</f>
         <v>1.8608314711153389E-3</v>
       </c>
       <c r="E18" s="7">
-        <f>IWDA!B33</f>
-        <v>4.501988307397565E-3</v>
+        <f>IWDA!B34</f>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <f>IWDA!I12</f>
@@ -2199,19 +2200,19 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C19" s="7">
         <f>EMIM!B28</f>
         <v>4.4786061793558284E-3</v>
       </c>
       <c r="D19" s="7">
-        <f>EMIM!B30</f>
+        <f>EMIM!B29</f>
         <v>1.3203125018091872E-3</v>
       </c>
       <c r="E19" s="7">
         <f>EMIM!B32</f>
-        <v>3.9380063083695798E-3</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
         <f>EMIM!H12</f>
@@ -2221,15 +2222,15 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C20" s="7">
         <f>IEMM!B28</f>
         <v>1.1411843296331416E-2</v>
       </c>
       <c r="E20" s="7">
-        <f>IEMM!B31</f>
-        <v>1.0872684125879233E-2</v>
+        <f>IEMM!B32</f>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <f>IEMM!I12</f>
@@ -2239,15 +2240,15 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C21" s="7">
         <f>IEMA!B28</f>
         <v>5.6395368492800409E-3</v>
       </c>
       <c r="E21" s="7">
-        <f>IEMA!B31</f>
-        <v>5.8880853206998689E-3</v>
+        <f>IEMA!B32</f>
+        <v>0</v>
       </c>
       <c r="F21" s="14">
         <f>IEMA!I12</f>
@@ -2257,15 +2258,15 @@
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C22" s="7">
         <f>IEMS!B28</f>
         <v>7.0185445283327264E-3</v>
       </c>
       <c r="E22" s="7">
-        <f>IEMS!B31</f>
-        <v>4.6104515530258783E-3</v>
+        <f>IEMS!B32</f>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <f>IEMS!I12</f>
@@ -2275,7 +2276,7 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C23" s="7">
         <f>IUSN!B28</f>
@@ -2285,9 +2286,9 @@
         <f>IUSN!B29</f>
         <v>3.6929567687143225E-3</v>
       </c>
-      <c r="E23" s="7">
-        <f>IUSN!B31</f>
-        <v>5.9432218800610885E-3</v>
+      <c r="E23" s="7" t="e">
+        <f>IUSN!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="F23" s="14">
         <f>IUSN!E12</f>
@@ -2297,12 +2298,12 @@
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C27" s="5">
         <f>C18*D5+C19*(D7+D8)+C23*D6</f>
@@ -2313,19 +2314,19 @@
       <c r="B28" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="5" t="e">
         <f>E18*D5+E19*(D7+D8)+E23*D6</f>
-        <v>4.5814807061193485E-3</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C31" s="5">
         <f>D18*D5+D19*(D7+D8)+D23*D6</f>
@@ -2334,19 +2335,19 @@
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C32" s="5">
         <f>(F18*D5+F19*(D7+D8)+F23*D6)*2.5%</f>
         <v>3.0011948778288109E-3</v>
       </c>
       <c r="D32" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C33" s="6">
         <f>SUM(C31:C32)</f>
@@ -2361,7 +2362,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:Q46"/>
+  <dimension ref="A2:Q42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.42578125" customWidth="1"/>
@@ -2670,7 +2671,7 @@
         <v>0.11813180456504087</v>
       </c>
       <c r="K12" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2710,12 +2711,12 @@
         <v>2.9552246149475263E-3</v>
       </c>
       <c r="K13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B14" s="29">
         <f>B10/B8</f>
@@ -2747,7 +2748,7 @@
       </c>
       <c r="I14" s="48"/>
       <c r="K14" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2788,38 +2789,38 @@
       </c>
       <c r="I16" s="28"/>
       <c r="K16" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="57">
+      <c r="B17" s="54">
         <f t="shared" ref="B17:H17" si="4">B16/B8</f>
         <v>8.1177520071364855E-6</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="54">
         <f t="shared" si="4"/>
         <v>1.3044290786768829E-4</v>
       </c>
-      <c r="D17" s="57">
+      <c r="D17" s="54">
         <f t="shared" si="4"/>
         <v>1.759568933481977E-4</v>
       </c>
-      <c r="E17" s="57">
+      <c r="E17" s="54">
         <f t="shared" si="4"/>
         <v>2.4884792626728109E-4</v>
       </c>
-      <c r="F17" s="57">
+      <c r="F17" s="54">
         <f t="shared" si="4"/>
         <v>2.5017762985677424E-4</v>
       </c>
-      <c r="G17" s="57">
+      <c r="G17" s="54">
         <f t="shared" si="4"/>
         <v>3.2264616277382854E-4</v>
       </c>
-      <c r="H17" s="57">
+      <c r="H17" s="54">
         <f t="shared" si="4"/>
         <v>2.7143394473084495E-4</v>
       </c>
@@ -2830,7 +2831,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B18" s="51">
         <f>3/B5</f>
@@ -2946,7 +2947,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B23" s="29"/>
       <c r="C23" s="29">
@@ -2987,7 +2988,7 @@
         <v>5.364067778665299E-3</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="D25" s="26"/>
       <c r="E25" s="26"/>
@@ -3003,11 +3004,11 @@
         <v>45</v>
       </c>
       <c r="B26" s="28">
-        <f>TrackingDifference!L5/100</f>
+        <f>TrackingDifference!M5/100</f>
         <v>5.0499999999999989E-3</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D26" s="18"/>
       <c r="E26" s="18"/>
@@ -3016,7 +3017,7 @@
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
       <c r="K26" s="8"/>
-      <c r="O26" s="59"/>
+      <c r="O26" s="56"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
@@ -3052,44 +3053,29 @@
         <v>3</v>
       </c>
       <c r="B29" s="26">
-        <f>G7+I13-H17+H21</f>
+        <f>H7+I13-H17+H21</f>
         <v>4.8160560860628652E-3</v>
       </c>
       <c r="J29" s="6"/>
       <c r="K29" s="8"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B30" s="34">
-        <f>B29-B25</f>
-        <v>-5.480116926024339E-4</v>
-      </c>
-      <c r="J30" s="6"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B31" s="30">
+      <c r="A30" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="30">
         <f>B29-I13</f>
         <v>1.8608314711153389E-3</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="8"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="34"/>
       <c r="J31" s="6"/>
-      <c r="O31" s="4"/>
-      <c r="Q31" s="60"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
       <c r="E32" s="12"/>
@@ -3098,15 +3084,12 @@
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="6"/>
+      <c r="O32" s="4"/>
+      <c r="Q32" s="57"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="12">
-        <f>B26+B30</f>
-        <v>4.501988307397565E-3</v>
-      </c>
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
       <c r="E33" s="12"/>
@@ -3118,7 +3101,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
+      <c r="B34" s="12"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
       <c r="E34" s="12"/>
@@ -3129,49 +3112,25 @@
       <c r="J34" s="6"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>79</v>
-      </c>
+      <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="12"/>
-      <c r="D35" s="52">
-        <v>17</v>
-      </c>
-      <c r="E35" s="52">
-        <v>163</v>
-      </c>
-      <c r="F35" s="53">
-        <v>304</v>
-      </c>
-      <c r="G35" s="54">
-        <v>1181</v>
-      </c>
-      <c r="H35" s="54"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="6"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>80</v>
-      </c>
+      <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="12"/>
-      <c r="D36" s="5">
-        <f>D35/D8</f>
-        <v>3.15867707172055E-6</v>
-      </c>
-      <c r="E36" s="5">
-        <f>E35/E8</f>
-        <v>1.9016508195765037E-5</v>
-      </c>
-      <c r="F36" s="5">
-        <f>F35/F8</f>
-        <v>2.2736621667102952E-5</v>
-      </c>
-      <c r="G36" s="5">
-        <f>G35/G8</f>
-        <v>6.8533294646743069E-5</v>
-      </c>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="6"/>
@@ -3190,13 +3149,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="6"/>
     </row>
@@ -3248,54 +3207,6 @@
       <c r="I42" s="5"/>
       <c r="J42" s="6"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="6"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="6"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="6"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="6"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -3305,7 +3216,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85662431-B8A3-40F8-9BF4-EC97DECEFC14}">
-  <dimension ref="A2:J36"/>
+  <dimension ref="A2:J32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.5703125" customWidth="1"/>
@@ -3335,7 +3246,7 @@
         <v>34</v>
       </c>
       <c r="J3" s="50" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -3413,7 +3324,7 @@
       </c>
       <c r="H6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -3514,7 +3425,7 @@
       </c>
       <c r="H10" s="2"/>
       <c r="J10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -3541,7 +3452,7 @@
       </c>
       <c r="H11" s="2"/>
       <c r="J11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -3577,7 +3488,7 @@
         <v>0.12767451727949905</v>
       </c>
       <c r="J12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -3623,7 +3534,7 @@
       <c r="G14" s="16"/>
       <c r="H14" s="2"/>
       <c r="J14" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -3686,7 +3597,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B17" s="31">
         <f>4406/B5</f>
@@ -3784,7 +3695,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B22" s="34">
         <v>6.9999999999999999E-4</v>
@@ -3825,7 +3736,7 @@
         <v>5.7205998709862621E-3</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I24" s="6"/>
     </row>
@@ -3834,11 +3745,11 @@
         <v>45</v>
       </c>
       <c r="B25" s="7">
-        <f>TrackingDifference!L12/100</f>
+        <f>TrackingDifference!M12/100</f>
         <v>5.1800000000000136E-3</v>
       </c>
       <c r="C25" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -3861,73 +3772,17 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" s="34">
-        <f>B28-B24</f>
-        <v>-1.2419936916304337E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B30" s="7">
+      <c r="A29" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" s="7">
         <f>B28-H13</f>
         <v>1.3203125018091872E-3</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" s="30">
-        <f>B25+B29</f>
-        <v>3.9380063083695798E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="52">
-        <v>4</v>
-      </c>
-      <c r="D35" s="52">
-        <v>74</v>
-      </c>
-      <c r="E35" s="53">
-        <v>302</v>
-      </c>
-      <c r="F35" s="54">
-        <v>492</v>
-      </c>
-      <c r="G35" s="54"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="5">
-        <f>C35/C8</f>
-        <v>3.1426775612822126E-6</v>
-      </c>
-      <c r="D36" s="5">
-        <f>D35/D8</f>
-        <v>2.2839506172839506E-5</v>
-      </c>
-      <c r="E36" s="5">
-        <f>E35/E8</f>
-        <v>4.288310803135295E-5</v>
-      </c>
-      <c r="F36" s="5">
-        <f>F35/F8</f>
-        <v>4.9469609371072343E-5</v>
-      </c>
-      <c r="G36" s="5"/>
+      <c r="A32" s="1"/>
+      <c r="B32" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3937,7 +3792,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46EB2121-1E5C-40E6-84C9-729FC25AD7CB}">
-  <dimension ref="A2:K31"/>
+  <dimension ref="A2:K32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -3968,7 +3823,7 @@
         <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -4126,7 +3981,7 @@
       </c>
       <c r="I8" s="30"/>
       <c r="K8" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -4166,7 +4021,7 @@
       </c>
       <c r="I10" s="7"/>
       <c r="K10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -4197,7 +4052,7 @@
       </c>
       <c r="I11" s="7"/>
       <c r="K11" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -4237,7 +4092,7 @@
         <v>0.14928432060421487</v>
       </c>
       <c r="K12" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -4277,7 +4132,7 @@
         <v>3.6999651622709466E-3</v>
       </c>
       <c r="K13" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -4318,7 +4173,7 @@
       </c>
       <c r="I15" s="7"/>
       <c r="K15" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -4360,7 +4215,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B17" s="31">
         <f>52694/B5</f>
@@ -4470,7 +4325,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B22" s="29"/>
       <c r="C22" s="29">
@@ -4521,7 +4376,7 @@
         <v>45</v>
       </c>
       <c r="B25" s="28">
-        <f>TrackingDifference!L25/100</f>
+        <f>TrackingDifference!M25/100</f>
         <v>5.2599999999999912E-3</v>
       </c>
       <c r="C25" t="s">
@@ -4551,25 +4406,19 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" s="7">
-        <f>B28-B24</f>
-        <v>-6.495484469741129E-4</v>
-      </c>
+      <c r="A29" s="19"/>
+      <c r="B29" s="30"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="7"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B31" s="30">
-        <f>B25+B29</f>
-        <v>4.6104515530258783E-3</v>
-      </c>
+      <c r="A31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4578,7 +4427,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3319A48F-C74C-4C2A-9714-F1A50A94B19B}">
-  <dimension ref="A2:G36"/>
+  <dimension ref="A2:G35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.28515625" customWidth="1"/>
@@ -4622,7 +4471,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4676,7 +4525,7 @@
         <v>3.5000000000000001E-3</v>
       </c>
       <c r="G7" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4715,7 +4564,7 @@
       <c r="C10" s="11">
         <v>12293</v>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="58">
         <v>17604</v>
       </c>
       <c r="G10" s="8"/>
@@ -4819,7 +4668,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B17" s="31">
         <v>6.0000000000000001E-3</v>
@@ -4880,7 +4729,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B22" s="7">
         <v>2.9999999999999997E-4</v>
@@ -4938,7 +4787,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B29" s="4">
         <f>B28-C13</f>
@@ -4958,20 +4807,14 @@
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" s="15">
-        <f>B28-0.05%</f>
-        <v>5.9432218800610885E-3</v>
-      </c>
+      <c r="A31" s="1"/>
+      <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -4979,6 +4822,7 @@
       <c r="F32" s="6"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -5001,14 +4845,6 @@
       <c r="E35" s="5"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="6"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5016,7 +4852,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C9A39DF-ECA7-4B8A-BED1-414B316C3BE0}">
-  <dimension ref="A2:K31"/>
+  <dimension ref="A2:K32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -5028,7 +4864,7 @@
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="9"/>
@@ -5044,7 +4880,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>35</v>
@@ -5076,7 +4912,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -5133,7 +4969,7 @@
         <v>29657</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -5201,7 +5037,7 @@
       </c>
       <c r="I8" s="30"/>
       <c r="K8" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -5241,7 +5077,7 @@
       </c>
       <c r="I10" s="7"/>
       <c r="K10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -5266,7 +5102,7 @@
       <c r="G11" s="11">
         <v>21015</v>
       </c>
-      <c r="H11" s="58">
+      <c r="H11" s="55">
         <v>23056</v>
       </c>
       <c r="I11" s="7"/>
@@ -5422,7 +5258,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B17" s="31">
         <f>283768/B5</f>
@@ -5530,7 +5366,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B22" s="29"/>
       <c r="C22" s="29">
@@ -5575,7 +5411,7 @@
         <v>1.1259159170452185E-2</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -5583,11 +5419,11 @@
         <v>45</v>
       </c>
       <c r="B25" s="28">
-        <f>TrackingDifference!L32/100</f>
+        <f>TrackingDifference!M32/100</f>
         <v>1.0720000000000002E-2</v>
       </c>
       <c r="C25" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -5613,25 +5449,19 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" s="7">
-        <f>B28-B24</f>
-        <v>1.526841258792308E-4</v>
-      </c>
+      <c r="A29" s="19"/>
+      <c r="B29" s="30"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="7"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B31" s="30">
-        <f>B25+B29</f>
-        <v>1.0872684125879233E-2</v>
-      </c>
+      <c r="A31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5641,7 +5471,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4E9972-EF6D-435D-B893-B5209367B0F1}">
-  <dimension ref="A2:K31"/>
+  <dimension ref="A2:K32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -5653,7 +5483,7 @@
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="9"/>
@@ -5672,7 +5502,7 @@
         <v>19</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -5755,7 +5585,7 @@
         <v>3674</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -5798,7 +5628,7 @@
         <v>329714.28571428568</v>
       </c>
       <c r="C8" s="11">
-        <f t="shared" ref="C8:H8" si="0">C6/C7</f>
+        <f t="shared" ref="C8:G8" si="0">C6/C7</f>
         <v>350294.11764705885</v>
       </c>
       <c r="D8" s="11">
@@ -5823,7 +5653,7 @@
       </c>
       <c r="I8" s="30"/>
       <c r="K8" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -6041,7 +5871,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B17" s="31">
         <f>12930/B5</f>
@@ -6151,7 +5981,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B22" s="29"/>
       <c r="C22" s="29">
@@ -6202,7 +6032,7 @@
         <v>45</v>
       </c>
       <c r="B25" s="28">
-        <f>TrackingDifference!L39/100</f>
+        <f>TrackingDifference!M39/100</f>
         <v>1.0259999999999991E-2</v>
       </c>
       <c r="C25" t="s">
@@ -6232,25 +6062,19 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" s="7">
-        <f>B28-B24</f>
-        <v>-4.3719146793001224E-3</v>
-      </c>
+      <c r="A29" s="19"/>
+      <c r="B29" s="30"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="7"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B31" s="30">
-        <f>B25+B29</f>
-        <v>5.8880853206998689E-3</v>
-      </c>
+      <c r="A31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6259,7 +6083,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F8993B4-587A-4EB9-885B-D46C1E7C06F6}">
-  <dimension ref="A2:I32"/>
+  <dimension ref="A2:I33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
@@ -6271,7 +6095,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="9"/>
@@ -6285,10 +6109,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -6308,10 +6132,10 @@
         <v>2019</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I4" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -6356,7 +6180,7 @@
         <v>4812</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -6383,7 +6207,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -6412,7 +6236,7 @@
       </c>
       <c r="G8" s="7"/>
       <c r="I8" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -6444,7 +6268,7 @@
       </c>
       <c r="G10" s="7"/>
       <c r="I10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -6528,7 +6352,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B14" s="4">
         <f>B10/B8</f>
@@ -6616,7 +6440,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B18" s="31">
         <f>56/B5</f>
@@ -6695,7 +6519,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B23" s="29">
         <v>0</v>
@@ -6732,7 +6556,7 @@
         <v>7.6092256916506958E-3</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -6740,11 +6564,11 @@
         <v>45</v>
       </c>
       <c r="B26" s="28">
-        <f>TrackingDifference!L46/100</f>
+        <f>TrackingDifference!M46/100</f>
         <v>6.6249999999999963E-3</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -6770,25 +6594,19 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B30" s="7">
-        <f>B29-B25</f>
-        <v>-2.2734808496824646E-4</v>
-      </c>
+      <c r="A30" s="19"/>
+      <c r="B30" s="30"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
+      <c r="A31" s="2"/>
+      <c r="B31" s="7"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" s="30">
-        <f>B26+B30</f>
-        <v>6.3976519150317499E-3</v>
-      </c>
+      <c r="A32" s="1"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
